--- a/data/MUSIC-CRIME-Q_RoB_assessment.xlsx
+++ b/data/MUSIC-CRIME-Q_RoB_assessment.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zannt\OneDrive\Github repos\Music_on_anxiety_depression_meta_analysis\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff2fba3d3057d582/Github repos/Music_on_anxiety_depression_meta_analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{591604EF-2BE7-4B9C-9E59-89943BA8083E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_A6C4EEFF08AA43A08CDC70A2F3610E41F186253C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69F208CC-A8C5-4169-80E9-99D89064C155}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="CRIME-Q Codebook" sheetId="3" r:id="rId3"/>
+    <sheet name="CRIME-Q Codebook" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRIME-Q Codebook'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CRIME-Q Codebook'!$A$1:$J$21</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -29,6 +43,8 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Codex</author>
+    <author>tc={38ED6C03-D625-4FD8-9D4A-95703BC423A2}</author>
+    <author>tc={60E8B5D3-9D3F-479F-858D-85B930476AEA}</author>
   </authors>
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -62,9 +78,9 @@
             <scheme val="minor"/>
           </rPr>
           <t>3X - Animals: Reporting
-Question: Are experimental animals sufficiently described?
+Question: Are the experimental animals used for the behavioral assays sufficiently described?
 Response options: Yes; Partly; No
-Yes: Reports species, strain/stock, sex, age/stage, body mass or weight range, supplier/source, and identifiable group sizes.
+Yes: Reports species, strain/stock, sex, age/stage, body mass or weight range, supplier/source, and identifiable group sizes for the animals used in the behavioral assays.
 Partly: Missing one or two key descriptors.
 No: Generic or seriously insufficient animal description.
 Decision rule: missing only supplier or body weight can be Partly rather than No if other descriptors are adequate.
@@ -83,11 +99,11 @@
             <scheme val="minor"/>
           </rPr>
           <t>3Y - Animals: Technical Quality
-Question: Were animal characteristics comparable between groups and appropriate for the music intervention?
+Question: Were animal characteristics comparable between music/control groups and appropriate for the behavioral assay and acoustic/music exposure?
 Response options: Yes; Partly; No
-Yes: Clear evidence of group balance, matching, blocking, or litter-balancing, and animals are appropriate for the stated aim.
+Yes: Clear evidence of group balance, matching, blocking, or litter-balancing for the behavioral comparison, and animals are appropriate for the stated behavioral assay and acoustic/music exposure.
 Partly: Likely comparable but incompletely documented.
-No: Baseline imbalance is shown and unaddressed, or the model is unsuitable.
+No: Baseline imbalance is shown and unaddressed for the behavioral comparison, or the animal model/stage is unsuitable for the behavioral assay or acoustic/music exposure.
 Decision rule: homogeneous animals plus randomization but no reported baseline balance or matching is Partly, not Yes.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
@@ -104,9 +120,9 @@
             <scheme val="minor"/>
           </rPr>
           <t>3Z - Selection Bias: Baseline Characteristics
-Question: Were relevant baseline characteristics balanced between music and control groups?
+Question: Were relevant baseline characteristics balanced between music and control groups for the behavioral comparison?
 Response options: Yes; No; Unclear; NA
-Yes: Arm-specific baseline data are balanced, or explicit matching, blocking, weight-balancing, or litter-balancing was used.
+Yes: Arm-specific baseline data relevant to the behavioral comparison are balanced, or explicit matching, blocking, weight-balancing, or litter-balancing was used.
 No: Baseline imbalance is documented and not addressed.
 Unclear: No arm-specific baseline data and no balancing procedure.
 Decision rule: randomization alone does not establish baseline balance.
@@ -125,9 +141,9 @@
             <scheme val="minor"/>
           </rPr>
           <t>4Y - Sample-Size Calculation
-Question: Did the study report an appropriate a priori sample-size calculation?
+Question: Did the study report an appropriate a priori sample-size calculation for the behavioral experiment?
 Response options: Yes; Partly; No
-Yes: Reports an a priori power/sample-size calculation with effect size, power, alpha, and appropriate test or design.
+Yes: Reports an a priori power/sample-size calculation for the behavioral experiment with effect size, power, alpha, and appropriate test or design.
 Partly: Calculation or justification is mentioned but incomplete.
 No: No sample-size calculation or justification.
 Decision rule: "based on prior studies" is not a full calculation.
@@ -146,11 +162,11 @@
             <scheme val="minor"/>
           </rPr>
           <t>5X - Music Intervention: Reporting
-Question: Is the music intervention described sufficiently for replication?
+Question: Is the in vivo acoustic/music exposure described sufficiently to replicate the behavioral experiment?
 Response options: Yes; Partly; No
-Yes: Reports music type/genre, specific stimulus where relevant, delivery method, exposure duration, frequency/schedule, timing relative to outcomes, volume/intensity in dB, control condition, and individual vs group exposure.
+Yes: Reports music type/genre, specific stimulus where relevant, playback source/hardware or delivery method, speaker/cage/room arrangement, exposure duration, frequency/schedule, timing relative to behavioral assays, volume/intensity in dB at the animal/cage when possible, control acoustic condition, and individual, cage-level, group, or room-level exposure.
 Partly: One or more core elements are missing or vague.
-No: Music and control conditions are insufficiently described.
+No: Music/acoustic exposure and control conditions are insufficiently described for behavioral replication.
 Decision rule: if sound level in dB is missing, score at most Partly.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
@@ -167,11 +183,11 @@
             <scheme val="minor"/>
           </rPr>
           <t>5Y - Music Intervention: Technical Quality
-Question: Does the music intervention design appear technically sound for the stated aim?
+Question: Does the acoustic/music exposure design appear technically sound for interpreting the behavioral outcomes?
 Response options: Yes; Partly; No
-Yes: Plausibly delivers distinct music versus control with no obvious acoustic cross-contamination, pseudoreplication, dose/volume confound, or timing flaw.
+Yes: Plausibly delivers distinct acoustic/music versus control exposure for the behavioral experiment with no obvious acoustic cross-contamination, cage/litter/room pseudoreplication, dose/volume confound, timing flaw, or handling/control-condition confound.
 Partly: Plausible, but key technical information is incomplete or cage/litter pseudoreplication is present but partially mitigated.
-No: Clear technical problem such as music and control in the same cage, genre confounded with volume/duration, one cage/litter per group, random timing, or other uncontrolled fatal confound.
+No: Clear technical problem for behavioral interpretation, such as music and control in the same cage, genre confounded with volume/duration, one cage/litter/room per group, random timing, untreated handling differences, or other uncontrolled fatal confound.
 Decision rule: if animals share cages/litters and analysis treats individuals as independent, score at most Partly. If there is only one cage/litter per group, score No. In perinatal designs, pups from one dam are not independent.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
@@ -188,7 +204,7 @@
             <scheme val="minor"/>
           </rPr>
           <t>5Z(1) - Selection Bias: Sequence Generation
-Question: Was allocation to groups generated by an appropriate random method?
+Question: Was allocation to behavioral music/control groups generated by an appropriate random method?
 Response options: Yes; No; Unclear; NA
 Yes: Random method is described and plausible.
 No: Clearly non-random method.
@@ -209,11 +225,11 @@
             <scheme val="minor"/>
           </rPr>
           <t>5Z(2) - Performance Bias: Random Housing
-Question: Were animals randomly housed or protected from cage/position effects?
+Question: Were animals/cages/rooms randomly housed or protected from acoustic, cage-position, room-position, or testing-position effects relevant to behavior?
 Response options: Yes; No; Unclear; NA
-Yes: Random cage placement, counterbalancing, rotation, room-swap, or explicit control of positional confounds.
-No: Treatment is confounded with room, shelf, rack, cage, or position without matching or counterbalancing.
-Unclear: Housing/cage position is insufficiently reported, or separate rooms are explicitly matched but not counterbalanced.
+Yes: Random cage/room/test placement, counterbalancing, rotation, room-swap, or explicit control of acoustic and positional confounds relevant to behavioral outcomes.
+No: Treatment is confounded with room, shelf, rack, cage, sound source, or testing position without matching or counterbalancing.
+Unclear: Housing/cage/room/test position is insufficiently reported, or separate acoustic exposure rooms are explicitly matched but not counterbalanced.
 Decision rule: separate music/control rooms with no matching or counterbalancing are No. Matched but separate rooms are Unclear. Same room without cage-position randomization is Unclear.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
@@ -230,9 +246,9 @@
             <scheme val="minor"/>
           </rPr>
           <t>5Z(3) - Detection Bias: Outcome Assessment
-Question: Were animals assessed by a pre-specified, unbiased selection rule?
+Question: Were animals included in the behavioral outcome assessment by a pre-specified, unbiased selection rule?
 Response options: Yes; No; Unclear; NA
-Yes: All allocated animals were tested at a pre-specified time, or a pre-specified rule was applied.
+Yes: All allocated animals were tested in the behavioral assay at a pre-specified time, or a pre-specified behavioral-assessment rule was applied.
 No: Selection for outcome assessment was based on post-allocation response, survival, behavior, or outcome-dependent criteria.
 Unclear: Selection procedure is insufficiently reported.
 Decision rule: fixed-time testing of all animals is Yes. Selecting animals because they show the target phenotype after allocation is No.
@@ -251,7 +267,7 @@
             <scheme val="minor"/>
           </rPr>
           <t>6X - Ethical Compliance
-Question: Did the study report compliance with animal-welfare regulations?
+Question: Did the study report animal-welfare compliance for the in vivo behavioral/music-exposure experiment?
 Response options: Yes; Partly; No
 Yes: Reports approval by an ethics, animal-care, or institutional committee, or gives a protocol number.
 Partly: Reports general animal-welfare guideline compliance without specific approval or protocol number.
@@ -271,10 +287,10 @@
             <scheme val="minor"/>
           </rPr>
           <t>7X - Blinding: Reporting
-Question: Does the report describe blinding in any phase?
+Question: Does the report describe blinding in a phase that can affect the behavioral outcomes or acoustic/music exposure?
 Response options: Yes; Partly; No
-Yes: States who was blinded, when, and to which condition.
-Partly: Mentions blinding but with limited detail.
+Yes: States who was blinded, when, and to which acoustic/music or behavioral condition.
+Partly: Mentions blinding for behavioral testing/scoring, acoustic exposure, or another directly relevant phase, but with limited detail.
 No: No mention of blinding.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
@@ -291,12 +307,12 @@
             <scheme val="minor"/>
           </rPr>
           <t>7Z(1) - Performance Bias: Experimenter Blinding
-Question: Were experimenters or handlers delivering music blinded to group assignment?
+Question: Were experimenters or handlers delivering acoustic/music exposure or behavioral testing blinded to group assignment where feasible?
 Response options: Yes; No; Unclear; NA
-Yes: Procedures prevented handlers from knowing group assignment.
+Yes: Procedures prevented exposure handlers, behavioral testers, or animal handlers from knowing group assignment in a way that could influence behavioral outcomes.
 No: Unblinded personnel could plausibly influence outcomes through differential handling, stress, or attention.
 Unclear: Not reported.
-NA: Explicitly justified as infeasible with otherwise identical automated delivery and handling.
+NA: Explicitly justified as infeasible for the acoustic/music exposure, with otherwise identical automated delivery, handling, and behavioral testing.
 Decision rule: silence on handler blinding is Unclear, not No.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
@@ -313,9 +329,9 @@
             <scheme val="minor"/>
           </rPr>
           <t>7Z(2) - Detection Bias: Assessor Blinding
-Question: Were outcome assessors blinded to group assignment?
+Question: Were assessors/coders/analysts of behavioral outcomes blinded to group assignment?
 Response options: Yes; No; Unclear; NA
-Yes: Assessors, coders, or analysts were blinded to assignment during assessment or analysis.
+Yes: Assessors, coders, or analysts were blinded to acoustic/music assignment during behavioral outcome assessment or analysis.
 No: Assessor was unblinded and the outcome is judgment-sensitive.
 Unclear: Not reported or unclear.
 Decision rule: blinding to genotype or another factor does not prove blinding to music/control condition.
@@ -334,11 +350,11 @@
             <scheme val="minor"/>
           </rPr>
           <t>8X - Methods-Results Alignment
-Question: Are reported methods and results coherent, transparent, and aligned?
+Question: Are behavioral-assay and acoustic-exposure methods/results coherent, transparent, and aligned?
 Response options: Yes; Partly; No
-Yes: Outcomes, group labels, n, timing, and statistical analyses match between Methods and Results.
+Yes: Behavioral outcomes, acoustic/music exposure groups, n, timing, and statistical analyses match between Methods and Results.
 Partly: Minor discrepancies, but primary comparisons are interpretable.
-No: Major mismatches, outcome switching, unreported contrasts, untraceable results, or serious internal numerical contradictions.
+No: Major behavioral or acoustic-exposure mismatches, outcome switching, unreported behavioral contrasts, untraceable results, or serious internal numerical contradictions.
 Decision rule: cross-check n in text, figures, tables, legends, and flow diagrams.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
@@ -355,12 +371,12 @@
             <scheme val="minor"/>
           </rPr>
           <t>8Z(1) - Attrition Bias: Incomplete Data
-Question: Were outcome data complete, with exclusions/attrition adequately handled?
+Question: Were behavioral outcome data complete, with exclusions/attrition adequately handled?
 Response options: Yes; No; Unclear
-Yes: Numbers allocated, analyzed, and excluded/lost are clear with reasons, or all allocated animals contributed data.
+Yes: Numbers allocated, analyzed for behavioral outcomes, and excluded/lost are clear with reasons, or all allocated animals contributed behavioral data.
 No: Missing/excluded animals are unequal, outcome-related, or unexplained.
 Unclear: Denominators or exclusion reasons are insufficient.
-Decision rule: if allocation n matches analysis n and no exclusions are reported, zero attrition is implied. If allocation n is never clear, Unclear.
+Decision rule: if allocation n matches analysis n and no exclusions are reported, zero attrition is implied. If allocation n is never clear, Unclear. Smaller molecular, histological, or biochemical subsets do not affect this item unless they also change which animals contributed behavioral outcomes.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
       </text>
@@ -376,11 +392,11 @@
             <scheme val="minor"/>
           </rPr>
           <t>8Z(2) - Reporting Bias: Selective Outcomes
-Question: Were all pre-specified or expected outcomes fully reported?
+Question: Were all pre-specified or expected behavioral outcomes fully reported?
 Response options: Yes; No; Unclear
-Yes: Pre-specified outcomes match reported outcomes, or Methods enumerate outcomes and Results report all with group-level statistics.
-No: Key outcome in Methods is missing from Results, outcome switching is evident, or favorable selective reporting is apparent.
-Unclear: Methods do not clearly pre-specify outcomes and no registration is available.
+Yes: Pre-specified behavioral outcomes match reported outcomes, or Methods enumerate behavioral outcomes and Results report all with group-level statistics.
+No: Key behavioral outcome in Methods is missing from Results, behavioral outcome switching is evident, or favorable selective behavioral reporting is apparent.
+Unclear: Methods do not clearly pre-specify behavioral outcomes and no registration is available.
 Decision rule: no registration alone does not force Unclear. A measured but dropped outcome counts against full reporting.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
@@ -397,12 +413,12 @@
             <scheme val="minor"/>
           </rPr>
           <t>9X - Discussion: Limitations
-Question: Did authors acknowledge relevant study limitations?
+Question: Did authors acknowledge limitations relevant to behavioral assays, acoustic/music delivery, exposure/control conditions, or interpretation of behavioral outcomes?
 Response options: Yes; Partly; No
-Yes: Substantive limitations linked to this study's experiment, model, measures, design, or interpretation.
-Partly: Generic or very brief limitation statement.
-No: No study-specific limitation.
-Decision rule: future-directions statements alone are not limitations.
+Yes: Substantive limitations linked to this study's behavioral assays, acoustic/music exposure, control condition, animal model, design, or interpretation of behavioral outcomes.
+Partly: One concrete but brief limitation in those areas, or a relevant limitation stated only generally.
+No: No study-specific limitation relevant to behavioral assays, acoustic/music exposure, control conditions, or behavioral interpretation.
+Decision rule: future-directions statements alone are not limitations. Mechanistic omissions, such as unmeasured biomarkers, hormones, histology, or molecular pathways, count only when the authors link them to interpretation of behavioral outcomes or the acoustic/music exposure.
 Source: CRIME-Q_CODEBOOK_FOR_NOTEBOOKLM.md</t>
         </r>
       </text>
@@ -446,12 +462,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="AT16" authorId="1" shapeId="0" xr:uid="{38ED6C03-D625-4FD8-9D4A-95703BC423A2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Didn't you limited the items to our particular outcomes of interest? this answer still included Golgi spine density
+Reply:
+    Or did you restrict that in the next items only?</t>
+      </text>
+    </comment>
+    <comment ref="AZ16" authorId="2" shapeId="0" xr:uid="{60E8B5D3-9D3F-479F-858D-85B930476AEA}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All outcomes
+</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="855">
   <si>
     <t>Study</t>
   </si>
@@ -957,10 +992,10 @@
     <t>[p.2-9] all behavioural and molecular outcomes reported with figures</t>
   </si>
   <si>
-    <t>Behavioural n=11 stated, but molecular subsets (N=4–6) are not reconciled to allocation.</t>
-  </si>
-  <si>
-    <t>[Fig 3] "N = 4 – 6 in each group"</t>
+    <t>Behavioral group size is stated and behavioral figures report N=11 per group; smaller molecular subsets are outside the behavioral attrition item under the revised scope.</t>
+  </si>
+  <si>
+    <t>[Fig. 1] "N = 11 in each group" and [Fig. 3] "N = 4 - 6 in each group" (molecular figure only).</t>
   </si>
   <si>
     <t>Methods enumerate behavioural and molecular outcomes; Results report all.</t>
@@ -1317,10 +1352,10 @@
     <t>[p.13] "the animals were divided in four groups"</t>
   </si>
   <si>
-    <t>Genre/composers, volume, duration, schedule and control condition specified.</t>
-  </si>
-  <si>
-    <t>[p.13] "Diverse musical pieces of various classical music composers including Bach, Chopin... Mozart... reproduced around 65dB... remained for 12 hours, with a 10-minute silent interval, every 30 minutes... three times a week during the dark cycle, three months"</t>
+    <t>Music type/composers, intensity, schedule, duration, and control condition are reported, but playback hardware and cage/room delivery arrangement are not described.</t>
+  </si>
+  <si>
+    <t>[p.13] "Diverse musical pieces of various classical music composers including Bach, Chopin... Mozart... reproduced around 65dB intensity levels... remained for 12 hours... three times a week during the dark cycle, three months on alternated days."</t>
   </si>
   <si>
     <t>8 animals per cage (pseudoreplication) and acoustic separation of music vs no-music groups not described.</t>
@@ -1668,10 +1703,10 @@
     <t>[p.321-325] EPM, SPT, FST, NORT and T-maze outcomes all reported</t>
   </si>
   <si>
-    <t>Acknowledges the study measured only behaviour (no mechanistic markers), but framed largely as future work.</t>
-  </si>
-  <si>
-    <t>[p.326] "There are some limitations of the present study... Further studies include, estimation of cortisol levels, neurotransmitter levels, BDNF, cytokine profiling and histological studies"</t>
+    <t>The limitations/future-work paragraph focuses on mechanistic biomarker and histology studies, not behavioral assay feasibility, acoustic delivery/control, or behavioral interpretation under the revised scope.</t>
+  </si>
+  <si>
+    <t>[p.326] "Further studies include, estimation of cortisol levels, neurotransmitter levels, Brain-derived neurotrophic factor (BDNF), cytokine profiling and histological studies..."</t>
   </si>
   <si>
     <t>[p.327] "Conflict of Interest: The authors declare that they have no competing interests"</t>
@@ -1740,18 +1775,21 @@
     <t>[Methods] "approved by the Animal Care and Use Committee of the School of Medicine of Shandong University"</t>
   </si>
   <si>
-    <t>States behavioural raters were blinded (to genotype).</t>
+    <t>Behavioral rater blinding is reported, but only to genotype; blinding to acoustic/music exposure is not stated.</t>
+  </si>
+  <si>
+    <t>[Methods] "All behavioral measurements were performed by raters blind to genotype."</t>
+  </si>
+  <si>
+    <t>No information on handler/delivery blinding to the acoustic condition.</t>
+  </si>
+  <si>
+    <t>Raters were blind to genotype, but blinding to the music/white-noise condition is not stated.</t>
   </si>
   <si>
     <t>[Methods] "All behavioral measurements were performed by raters blind to genotype"</t>
   </si>
   <si>
-    <t>No information on handler/delivery blinding to the acoustic condition.</t>
-  </si>
-  <si>
-    <t>Raters were blind to genotype, but blinding to the music/white-noise condition is not stated.</t>
-  </si>
-  <si>
     <t>Methods (open field, EPM, BDNF ELISA) and Results align across genotypes.</t>
   </si>
   <si>
@@ -2454,10 +2492,10 @@
     <t>[p.2-3] open field, Morris water maze and passive avoidance tests described and reported</t>
   </si>
   <si>
-    <t>The authors briefly identify that the mechanism of music's effect was not studied and call for further mechanistic work; this is a study-specific limitation, though brief.</t>
-  </si>
-  <si>
-    <t>[p.7, Conclusions] "the mechanism by which music alleviated the impairments induced by SPS in rats is not studied. Further studies... are needed"</t>
+    <t>The stated limitation is that the neural mechanism was not studied; no limitation is given for behavioral assays, acoustic exposure/control, or behavioral interpretation under the revised scope.</t>
+  </si>
+  <si>
+    <t>[p.7] "the mechanism by which music alleviated the impairments induced by SPS in rats is not studied."</t>
   </si>
   <si>
     <t>[p.7782] "Conflicts of Interest: The authors declare no conflict of interest"</t>
@@ -2532,10 +2570,10 @@
     <t>[Results] elevated plus maze and open field outcomes reported across developmental ages</t>
   </si>
   <si>
-    <t>The authors explicitly discuss study-specific caveats, including unmeasured hormones and possible adaptation/test-repetition effects.</t>
-  </si>
-  <si>
-    <t>[p.184-186, Discussion/Conclusions] "hormone levels... were not measured in our study" and "it cannot be discarded that these effects might have been due to the animals' adaptation to the tests..."</t>
+    <t>One behavioral-assay limitation remains: possible adaptation from repeating the same tests at later developmental stages. The unmeasured hormone caveat is mechanistic and no longer drives this item.</t>
+  </si>
+  <si>
+    <t>[p.186] "it cannot be discarded that these effects might have been due to the animals' adaptation to the tests because the same test was reapplied at each developmental stage."</t>
   </si>
   <si>
     <t>Terzioglu2020</t>
@@ -2679,13 +2717,13 @@
     <t>Animals: Reporting</t>
   </si>
   <si>
-    <t>Are experimental animals sufficiently described?</t>
+    <t>Are the experimental animals used for the behavioral assays sufficiently described?</t>
   </si>
   <si>
     <t>Yes; Partly; No</t>
   </si>
   <si>
-    <t>Reports species, strain/stock, sex, age/stage, body mass or weight range, supplier/source, and identifiable group sizes.</t>
+    <t>Reports species, strain/stock, sex, age/stage, body mass or weight range, supplier/source, and identifiable group sizes for the animals used in the behavioral assays.</t>
   </si>
   <si>
     <t>Missing one or two key descriptors.</t>
@@ -2700,16 +2738,16 @@
     <t>Animals: Technical Quality</t>
   </si>
   <si>
-    <t>Were animal characteristics comparable between groups and appropriate for the music intervention?</t>
-  </si>
-  <si>
-    <t>Clear evidence of group balance, matching, blocking, or litter-balancing, and animals are appropriate for the stated aim.</t>
+    <t>Were animal characteristics comparable between music/control groups and appropriate for the behavioral assay and acoustic/music exposure?</t>
+  </si>
+  <si>
+    <t>Clear evidence of group balance, matching, blocking, or litter-balancing for the behavioral comparison, and animals are appropriate for the stated behavioral assay and acoustic/music exposure.</t>
   </si>
   <si>
     <t>Likely comparable but incompletely documented.</t>
   </si>
   <si>
-    <t>Baseline imbalance is shown and unaddressed, or the model is unsuitable.</t>
+    <t>Baseline imbalance is shown and unaddressed for the behavioral comparison, or the animal model/stage is unsuitable for the behavioral assay or acoustic/music exposure.</t>
   </si>
   <si>
     <t>homogeneous animals plus randomization but no reported baseline balance or matching is Partly, not Yes.</t>
@@ -2718,13 +2756,13 @@
     <t>Selection Bias: Baseline Characteristics</t>
   </si>
   <si>
-    <t>Were relevant baseline characteristics balanced between music and control groups?</t>
+    <t>Were relevant baseline characteristics balanced between music and control groups for the behavioral comparison?</t>
   </si>
   <si>
     <t>Yes; No; Unclear; NA</t>
   </si>
   <si>
-    <t>Arm-specific baseline data are balanced, or explicit matching, blocking, weight-balancing, or litter-balancing was used.</t>
+    <t>Arm-specific baseline data relevant to the behavioral comparison are balanced, or explicit matching, blocking, weight-balancing, or litter-balancing was used.</t>
   </si>
   <si>
     <t>Baseline imbalance is documented and not addressed.</t>
@@ -2739,10 +2777,10 @@
     <t>Sample-Size Calculation</t>
   </si>
   <si>
-    <t>Did the study report an appropriate a priori sample-size calculation?</t>
-  </si>
-  <si>
-    <t>Reports an a priori power/sample-size calculation with effect size, power, alpha, and appropriate test or design.</t>
+    <t>Did the study report an appropriate a priori sample-size calculation for the behavioral experiment?</t>
+  </si>
+  <si>
+    <t>Reports an a priori power/sample-size calculation for the behavioral experiment with effect size, power, alpha, and appropriate test or design.</t>
   </si>
   <si>
     <t>Calculation or justification is mentioned but incomplete.</t>
@@ -2757,16 +2795,16 @@
     <t>Music Intervention: Reporting</t>
   </si>
   <si>
-    <t>Is the music intervention described sufficiently for replication?</t>
-  </si>
-  <si>
-    <t>Reports music type/genre, specific stimulus where relevant, delivery method, exposure duration, frequency/schedule, timing relative to outcomes, volume/intensity in dB, control condition, and individual vs group exposure.</t>
+    <t>Is the in vivo acoustic/music exposure described sufficiently to replicate the behavioral experiment?</t>
+  </si>
+  <si>
+    <t>Reports music type/genre, specific stimulus where relevant, playback source/hardware or delivery method, speaker/cage/room arrangement, exposure duration, frequency/schedule, timing relative to behavioral assays, volume/intensity in dB at the animal/cage when possible, control acoustic condition, and individual, cage-level, group, or room-level exposure.</t>
   </si>
   <si>
     <t>One or more core elements are missing or vague.</t>
   </si>
   <si>
-    <t>Music and control conditions are insufficiently described.</t>
+    <t>Music/acoustic exposure and control conditions are insufficiently described for behavioral replication.</t>
   </si>
   <si>
     <t>if sound level in dB is missing, score at most Partly.</t>
@@ -2775,16 +2813,16 @@
     <t>Music Intervention: Technical Quality</t>
   </si>
   <si>
-    <t>Does the music intervention design appear technically sound for the stated aim?</t>
-  </si>
-  <si>
-    <t>Plausibly delivers distinct music versus control with no obvious acoustic cross-contamination, pseudoreplication, dose/volume confound, or timing flaw.</t>
+    <t>Does the acoustic/music exposure design appear technically sound for interpreting the behavioral outcomes?</t>
+  </si>
+  <si>
+    <t>Plausibly delivers distinct acoustic/music versus control exposure for the behavioral experiment with no obvious acoustic cross-contamination, cage/litter/room pseudoreplication, dose/volume confound, timing flaw, or handling/control-condition confound.</t>
   </si>
   <si>
     <t>Plausible, but key technical information is incomplete or cage/litter pseudoreplication is present but partially mitigated.</t>
   </si>
   <si>
-    <t>Clear technical problem such as music and control in the same cage, genre confounded with volume/duration, one cage/litter per group, random timing, or other uncontrolled fatal confound.</t>
+    <t>Clear technical problem for behavioral interpretation, such as music and control in the same cage, genre confounded with volume/duration, one cage/litter/room per group, random timing, untreated handling differences, or other uncontrolled fatal confound.</t>
   </si>
   <si>
     <t>if animals share cages/litters and analysis treats individuals as independent, score at most Partly. If there is only one cage/litter per group, score No. In perinatal designs, pups from one dam are not independent.</t>
@@ -2793,7 +2831,7 @@
     <t>Selection Bias: Sequence Generation</t>
   </si>
   <si>
-    <t>Was allocation to groups generated by an appropriate random method?</t>
+    <t>Was allocation to behavioral music/control groups generated by an appropriate random method?</t>
   </si>
   <si>
     <t>Random method is described and plausible.</t>
@@ -2811,16 +2849,16 @@
     <t>Performance Bias: Random Housing</t>
   </si>
   <si>
-    <t>Were animals randomly housed or protected from cage/position effects?</t>
-  </si>
-  <si>
-    <t>Random cage placement, counterbalancing, rotation, room-swap, or explicit control of positional confounds.</t>
-  </si>
-  <si>
-    <t>Treatment is confounded with room, shelf, rack, cage, or position without matching or counterbalancing.</t>
-  </si>
-  <si>
-    <t>Housing/cage position is insufficiently reported, or separate rooms are explicitly matched but not counterbalanced.</t>
+    <t>Were animals/cages/rooms randomly housed or protected from acoustic, cage-position, room-position, or testing-position effects relevant to behavior?</t>
+  </si>
+  <si>
+    <t>Random cage/room/test placement, counterbalancing, rotation, room-swap, or explicit control of acoustic and positional confounds relevant to behavioral outcomes.</t>
+  </si>
+  <si>
+    <t>Treatment is confounded with room, shelf, rack, cage, sound source, or testing position without matching or counterbalancing.</t>
+  </si>
+  <si>
+    <t>Housing/cage/room/test position is insufficiently reported, or separate acoustic exposure rooms are explicitly matched but not counterbalanced.</t>
   </si>
   <si>
     <t>separate music/control rooms with no matching or counterbalancing are No. Matched but separate rooms are Unclear. Same room without cage-position randomization is Unclear.</t>
@@ -2829,10 +2867,10 @@
     <t>Detection Bias: Outcome Assessment</t>
   </si>
   <si>
-    <t>Were animals assessed by a pre-specified, unbiased selection rule?</t>
-  </si>
-  <si>
-    <t>All allocated animals were tested at a pre-specified time, or a pre-specified rule was applied.</t>
+    <t>Were animals included in the behavioral outcome assessment by a pre-specified, unbiased selection rule?</t>
+  </si>
+  <si>
+    <t>All allocated animals were tested in the behavioral assay at a pre-specified time, or a pre-specified behavioral-assessment rule was applied.</t>
   </si>
   <si>
     <t>Selection for outcome assessment was based on post-allocation response, survival, behavior, or outcome-dependent criteria.</t>
@@ -2847,7 +2885,7 @@
     <t>Ethical Compliance</t>
   </si>
   <si>
-    <t>Did the study report compliance with animal-welfare regulations?</t>
+    <t>Did the study report animal-welfare compliance for the in vivo behavioral/music-exposure experiment?</t>
   </si>
   <si>
     <t>Reports approval by an ethics, animal-care, or institutional committee, or gives a protocol number.</t>
@@ -2862,13 +2900,13 @@
     <t>Blinding: Reporting</t>
   </si>
   <si>
-    <t>Does the report describe blinding in any phase?</t>
-  </si>
-  <si>
-    <t>States who was blinded, when, and to which condition.</t>
-  </si>
-  <si>
-    <t>Mentions blinding but with limited detail.</t>
+    <t>Does the report describe blinding in a phase that can affect the behavioral outcomes or acoustic/music exposure?</t>
+  </si>
+  <si>
+    <t>States who was blinded, when, and to which acoustic/music or behavioral condition.</t>
+  </si>
+  <si>
+    <t>Mentions blinding for behavioral testing/scoring, acoustic exposure, or another directly relevant phase, but with limited detail.</t>
   </si>
   <si>
     <t>No mention of blinding.</t>
@@ -2877,10 +2915,10 @@
     <t>Performance Bias: Experimenter Blinding</t>
   </si>
   <si>
-    <t>Were experimenters or handlers delivering music blinded to group assignment?</t>
-  </si>
-  <si>
-    <t>Procedures prevented handlers from knowing group assignment.</t>
+    <t>Were experimenters or handlers delivering acoustic/music exposure or behavioral testing blinded to group assignment where feasible?</t>
+  </si>
+  <si>
+    <t>Procedures prevented exposure handlers, behavioral testers, or animal handlers from knowing group assignment in a way that could influence behavioral outcomes.</t>
   </si>
   <si>
     <t>Unblinded personnel could plausibly influence outcomes through differential handling, stress, or attention.</t>
@@ -2889,7 +2927,7 @@
     <t>Not reported.</t>
   </si>
   <si>
-    <t>Explicitly justified as infeasible with otherwise identical automated delivery and handling.</t>
+    <t>Explicitly justified as infeasible for the acoustic/music exposure, with otherwise identical automated delivery, handling, and behavioral testing.</t>
   </si>
   <si>
     <t>silence on handler blinding is Unclear, not No.</t>
@@ -2898,10 +2936,10 @@
     <t>Detection Bias: Assessor Blinding</t>
   </si>
   <si>
-    <t>Were outcome assessors blinded to group assignment?</t>
-  </si>
-  <si>
-    <t>Assessors, coders, or analysts were blinded to assignment during assessment or analysis.</t>
+    <t>Were assessors/coders/analysts of behavioral outcomes blinded to group assignment?</t>
+  </si>
+  <si>
+    <t>Assessors, coders, or analysts were blinded to acoustic/music assignment during behavioral outcome assessment or analysis.</t>
   </si>
   <si>
     <t>Assessor was unblinded and the outcome is judgment-sensitive.</t>
@@ -2916,16 +2954,16 @@
     <t>Methods-Results Alignment</t>
   </si>
   <si>
-    <t>Are reported methods and results coherent, transparent, and aligned?</t>
-  </si>
-  <si>
-    <t>Outcomes, group labels, n, timing, and statistical analyses match between Methods and Results.</t>
+    <t>Are behavioral-assay and acoustic-exposure methods/results coherent, transparent, and aligned?</t>
+  </si>
+  <si>
+    <t>Behavioral outcomes, acoustic/music exposure groups, n, timing, and statistical analyses match between Methods and Results.</t>
   </si>
   <si>
     <t>Minor discrepancies, but primary comparisons are interpretable.</t>
   </si>
   <si>
-    <t>Major mismatches, outcome switching, unreported contrasts, untraceable results, or serious internal numerical contradictions.</t>
+    <t>Major behavioral or acoustic-exposure mismatches, outcome switching, unreported behavioral contrasts, untraceable results, or serious internal numerical contradictions.</t>
   </si>
   <si>
     <t>cross-check n in text, figures, tables, legends, and flow diagrams.</t>
@@ -2934,13 +2972,13 @@
     <t>Attrition Bias: Incomplete Data</t>
   </si>
   <si>
-    <t>Were outcome data complete, with exclusions/attrition adequately handled?</t>
+    <t>Were behavioral outcome data complete, with exclusions/attrition adequately handled?</t>
   </si>
   <si>
     <t>Yes; No; Unclear</t>
   </si>
   <si>
-    <t>Numbers allocated, analyzed, and excluded/lost are clear with reasons, or all allocated animals contributed data.</t>
+    <t>Numbers allocated, analyzed for behavioral outcomes, and excluded/lost are clear with reasons, or all allocated animals contributed behavioral data.</t>
   </si>
   <si>
     <t>Missing/excluded animals are unequal, outcome-related, or unexplained.</t>
@@ -2949,22 +2987,22 @@
     <t>Denominators or exclusion reasons are insufficient.</t>
   </si>
   <si>
-    <t>if allocation n matches analysis n and no exclusions are reported, zero attrition is implied. If allocation n is never clear, Unclear.</t>
+    <t>if allocation n matches analysis n and no exclusions are reported, zero attrition is implied. If allocation n is never clear, Unclear. Smaller molecular, histological, or biochemical subsets do not affect this item unless they also change which animals contributed behavioral outcomes.</t>
   </si>
   <si>
     <t>Reporting Bias: Selective Outcomes</t>
   </si>
   <si>
-    <t>Were all pre-specified or expected outcomes fully reported?</t>
-  </si>
-  <si>
-    <t>Pre-specified outcomes match reported outcomes, or Methods enumerate outcomes and Results report all with group-level statistics.</t>
-  </si>
-  <si>
-    <t>Key outcome in Methods is missing from Results, outcome switching is evident, or favorable selective reporting is apparent.</t>
-  </si>
-  <si>
-    <t>Methods do not clearly pre-specify outcomes and no registration is available.</t>
+    <t>Were all pre-specified or expected behavioral outcomes fully reported?</t>
+  </si>
+  <si>
+    <t>Pre-specified behavioral outcomes match reported outcomes, or Methods enumerate behavioral outcomes and Results report all with group-level statistics.</t>
+  </si>
+  <si>
+    <t>Key behavioral outcome in Methods is missing from Results, behavioral outcome switching is evident, or favorable selective behavioral reporting is apparent.</t>
+  </si>
+  <si>
+    <t>Methods do not clearly pre-specify behavioral outcomes and no registration is available.</t>
   </si>
   <si>
     <t>no registration alone does not force Unclear. A measured but dropped outcome counts against full reporting.</t>
@@ -2973,19 +3011,19 @@
     <t>Discussion: Limitations</t>
   </si>
   <si>
-    <t>Did authors acknowledge relevant study limitations?</t>
-  </si>
-  <si>
-    <t>Substantive limitations linked to this study's experiment, model, measures, design, or interpretation.</t>
-  </si>
-  <si>
-    <t>Generic or very brief limitation statement.</t>
-  </si>
-  <si>
-    <t>No study-specific limitation.</t>
-  </si>
-  <si>
-    <t>future-directions statements alone are not limitations.</t>
+    <t>Did authors acknowledge limitations relevant to behavioral assays, acoustic/music delivery, exposure/control conditions, or interpretation of behavioral outcomes?</t>
+  </si>
+  <si>
+    <t>Substantive limitations linked to this study's behavioral assays, acoustic/music exposure, control condition, animal model, design, or interpretation of behavioral outcomes.</t>
+  </si>
+  <si>
+    <t>One concrete but brief limitation in those areas, or a relevant limitation stated only generally.</t>
+  </si>
+  <si>
+    <t>No study-specific limitation relevant to behavioral assays, acoustic/music exposure, control conditions, or behavioral interpretation.</t>
+  </si>
+  <si>
+    <t>future-directions statements alone are not limitations. Mechanistic omissions, such as unmeasured biomarkers, hormones, histology, or molecular pathways, count only when the authors link them to interpretation of behavioral outcomes or the acoustic/music exposure.</t>
   </si>
   <si>
     <t>Conflict-of-Interest Statement</t>
@@ -3019,7 +3057,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3110,12 +3148,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3143,6 +3175,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3158,6 +3196,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Guest User" id="{F4CB867C-D7A1-4DE4-8B1B-F2F9F306CDA5}" userId="" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3475,16 +3519,31 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="AT16" dT="2026-07-21T20:09:11.41" personId="{F4CB867C-D7A1-4DE4-8B1B-F2F9F306CDA5}" id="{38ED6C03-D625-4FD8-9D4A-95703BC423A2}">
+    <text>Didn't you limited the items to our particular outcomes of interest? this answer still included Golgi spine density</text>
+  </threadedComment>
+  <threadedComment ref="AT16" dT="2026-07-21T20:10:57.31" personId="{F4CB867C-D7A1-4DE4-8B1B-F2F9F306CDA5}" id="{D89B0B8F-66F3-4118-AFD8-6853DB79C6F1}" parentId="{38ED6C03-D625-4FD8-9D4A-95703BC423A2}">
+    <text>Or did you restrict that in the next items only?</text>
+  </threadedComment>
+  <threadedComment ref="AZ16" dT="2026-07-21T20:14:51.79" personId="{F4CB867C-D7A1-4DE4-8B1B-F2F9F306CDA5}" id="{60E8B5D3-9D3F-479F-858D-85B930476AEA}">
+    <text xml:space="preserve">All outcomes
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BJ21"/>
-  <sheetFormatPr defaultColWidth="30.54296875" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="30.5703125" defaultRowHeight="60" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="30.54296875" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="30.54296875" style="4"/>
+    <col min="1" max="2" width="30.5703125" style="4" customWidth="1"/>
+    <col min="3" max="16384" width="30.5703125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:62" ht="60" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3672,3786 +3731,3777 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:62" ht="60" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="15" t="s">
+      <c r="F2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="M2" s="15" t="s">
+      <c r="L2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="S2" s="15" t="s">
+      <c r="R2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="15" t="s">
+      <c r="T2" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="V2" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="W2" s="15" t="s">
+      <c r="W2" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="X2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y2" s="15" t="s">
+      <c r="X2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y2" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="Z2" s="15" t="s">
+      <c r="Z2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB2" s="15" t="s">
+      <c r="AA2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AC2" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AD2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AD2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE2" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AF2" s="15" t="s">
+      <c r="AF2" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="AG2" s="8" t="s">
+      <c r="AG2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AH2" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AI2" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="AJ2" s="8" t="s">
+      <c r="AJ2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AK2" s="15" t="s">
+      <c r="AK2" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="AL2" s="15" t="s">
+      <c r="AL2" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="AM2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN2" s="15" t="s">
+      <c r="AM2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN2" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AO2" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP2" s="10" t="s">
+      <c r="AP2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="AQ2" s="15" t="s">
+      <c r="AQ2" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="AR2" s="15" t="s">
+      <c r="AR2" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AS2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT2" s="15" t="s">
+      <c r="AS2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT2" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AU2" s="15" t="s">
+      <c r="AU2" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="AV2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW2" s="15" t="s">
+      <c r="AV2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW2" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="15" t="s">
+      <c r="AX2" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AY2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ2" s="15" t="s">
+      <c r="AY2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="BA2" s="15" t="s">
+      <c r="BA2" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="BB2" s="8" t="s">
+      <c r="BB2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BC2" s="15" t="s">
+      <c r="BC2" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="BD2" s="15" t="s">
+      <c r="BD2" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BE2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF2" s="15" t="s">
+      <c r="BE2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF2" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" s="15" t="s">
+      <c r="BG2" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI2" s="15" t="s">
+      <c r="BH2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI2" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BJ2" s="15" t="s">
+      <c r="BJ2" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:62" ht="60" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="C3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="M3" s="15" t="s">
+      <c r="L3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="R3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="S3" s="15" t="s">
+      <c r="R3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S3" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="T3" s="15" t="s">
+      <c r="T3" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="V3" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="15" t="s">
+      <c r="W3" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="X3" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y3" s="15" t="s">
+      <c r="X3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y3" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="Z3" s="15" t="s">
+      <c r="Z3" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="AA3" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB3" s="15" t="s">
+      <c r="AA3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB3" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AC3" s="15" t="s">
+      <c r="AC3" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="AD3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE3" s="15" t="s">
+      <c r="AD3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE3" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="AF3" s="15" t="s">
+      <c r="AF3" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="AG3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH3" s="15" t="s">
+      <c r="AG3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH3" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="AI3" s="15" t="s">
+      <c r="AI3" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="AJ3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK3" s="15" t="s">
+      <c r="AJ3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK3" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="AL3" s="15" t="s">
+      <c r="AL3" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="AM3" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN3" s="15" t="s">
+      <c r="AM3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN3" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="AO3" s="15" t="s">
+      <c r="AO3" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AQ3" s="15" t="s">
+      <c r="AP3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ3" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AR3" s="15" t="s">
+      <c r="AR3" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AS3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT3" s="15" t="s">
+      <c r="AS3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT3" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AU3" s="15" t="s">
+      <c r="AU3" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="AV3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW3" s="15" t="s">
+      <c r="AV3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW3" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="AX3" s="15" t="s">
+      <c r="AX3" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="AY3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ3" s="15" t="s">
+      <c r="AY3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ3" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="BA3" s="15" t="s">
+      <c r="BA3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="BB3" s="8" t="s">
+      <c r="BB3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BC3" s="15" t="s">
+      <c r="BC3" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="BD3" s="15" t="s">
+      <c r="BD3" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="BE3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF3" s="15" t="s">
+      <c r="BE3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF3" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="BG3" s="15" t="s">
+      <c r="BG3" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="BH3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI3" s="15" t="s">
+      <c r="BH3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI3" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="BJ3" s="15" t="s">
+      <c r="BJ3" s="13" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:62" ht="60" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>146</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="C4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="L4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="M4" s="15" t="s">
+      <c r="L4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="Q4" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="R4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="U4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="W4" s="15" t="s">
+      <c r="W4" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="X4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y4" s="15" t="s">
+      <c r="X4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y4" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="Z4" s="15" t="s">
+      <c r="Z4" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AA4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB4" s="15" t="s">
+      <c r="AA4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB4" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="AC4" s="15" t="s">
+      <c r="AC4" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AD4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE4" s="15" t="s">
+      <c r="AD4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE4" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AF4" s="15" t="s">
+      <c r="AF4" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AG4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH4" s="15" t="s">
+      <c r="AG4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH4" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="AI4" s="15" t="s">
+      <c r="AI4" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="AJ4" s="10" t="s">
+      <c r="AJ4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="AK4" s="15" t="s">
+      <c r="AK4" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="AL4" s="15" t="s">
+      <c r="AL4" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AM4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN4" s="15" t="s">
+      <c r="AM4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN4" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO4" s="15" t="s">
+      <c r="AO4" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ4" s="15" t="s">
+      <c r="AP4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ4" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="AR4" s="15" t="s">
+      <c r="AR4" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AS4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT4" s="15" t="s">
+      <c r="AS4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT4" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="AU4" s="15" t="s">
+      <c r="AU4" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="AV4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AW4" s="15" t="s">
+      <c r="AV4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW4" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="AX4" s="15" t="s">
+      <c r="AX4" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="AY4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ4" s="15" t="s">
+      <c r="AY4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ4" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="BA4" s="15" t="s">
+      <c r="BA4" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="BB4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC4" s="15" t="s">
+      <c r="BB4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC4" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="BD4" s="15" t="s">
+      <c r="BD4" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="BE4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF4" s="15" t="s">
+      <c r="BE4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF4" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="BG4" s="15" t="s">
+      <c r="BG4" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="BH4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI4" s="15" t="s">
+      <c r="BH4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI4" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="BJ4" s="15" t="s">
+      <c r="BJ4" s="13" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:62" ht="60" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="L5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="M5" s="15" t="s">
+      <c r="L5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="N5" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="R5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="S5" s="15" t="s">
+      <c r="R5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="T5" s="15" t="s">
+      <c r="T5" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="U5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="15" t="s">
+      <c r="V5" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="W5" s="15" t="s">
+      <c r="W5" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="X5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y5" s="15" t="s">
+      <c r="X5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y5" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="Z5" s="15" t="s">
+      <c r="Z5" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="AA5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB5" s="15" t="s">
+      <c r="AA5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB5" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="AC5" s="15" t="s">
+      <c r="AC5" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="AD5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE5" s="15" t="s">
+      <c r="AD5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE5" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="AF5" s="15" t="s">
+      <c r="AF5" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="AG5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH5" s="15" t="s">
+      <c r="AG5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH5" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="AI5" s="15" t="s">
+      <c r="AI5" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="AJ5" s="10" t="s">
+      <c r="AJ5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="AK5" s="15" t="s">
+      <c r="AK5" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="AL5" s="15" t="s">
+      <c r="AL5" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="AM5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN5" s="15" t="s">
+      <c r="AM5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN5" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO5" s="15" t="s">
+      <c r="AO5" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ5" s="15" t="s">
+      <c r="AP5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ5" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="AR5" s="15" t="s">
+      <c r="AR5" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="AS5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT5" s="15" t="s">
+      <c r="AS5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT5" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="AU5" s="15" t="s">
+      <c r="AU5" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AV5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AW5" s="15" t="s">
+      <c r="AV5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW5" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="AX5" s="15" t="s">
+      <c r="AX5" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AY5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ5" s="15" t="s">
+      <c r="AY5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ5" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="BA5" s="15" t="s">
+      <c r="BA5" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="BB5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC5" s="15" t="s">
+      <c r="BB5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC5" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="BD5" s="15" t="s">
+      <c r="BD5" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="BE5" s="10" t="s">
+      <c r="BE5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="BF5" s="15" t="s">
+      <c r="BF5" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="BG5" s="15" t="s">
+      <c r="BG5" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BH5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI5" s="15" t="s">
+      <c r="BH5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI5" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="BJ5" s="15" t="s">
+      <c r="BJ5" s="13" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:62" ht="60" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>215</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="15" t="s">
+      <c r="C6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="L6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" s="15" t="s">
+      <c r="L6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N6" s="15" t="s">
+      <c r="N6" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="P6" s="15" t="s">
+      <c r="P6" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q6" s="15" t="s">
+      <c r="Q6" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="S6" s="15" t="s">
+      <c r="R6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S6" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="T6" s="15" t="s">
+      <c r="T6" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="U6" s="8" t="s">
+      <c r="U6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="15" t="s">
+      <c r="V6" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="W6" s="15" t="s">
+      <c r="W6" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y6" s="15" t="s">
+      <c r="X6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y6" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="Z6" s="15" t="s">
+      <c r="Z6" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="AA6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB6" s="15" t="s">
+      <c r="AA6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB6" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="AC6" s="15" t="s">
+      <c r="AC6" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="AD6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE6" s="15" t="s">
+      <c r="AD6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE6" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="AF6" s="15" t="s">
+      <c r="AF6" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="AG6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH6" s="15" t="s">
+      <c r="AG6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH6" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="AI6" s="15" t="s">
+      <c r="AI6" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="AJ6" s="10" t="s">
+      <c r="AJ6" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="AK6" s="15" t="s">
+      <c r="AK6" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="AL6" s="15" t="s">
+      <c r="AL6" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AM6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN6" s="15" t="s">
+      <c r="AM6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN6" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO6" s="15" t="s">
+      <c r="AO6" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ6" s="15" t="s">
+      <c r="AP6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ6" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="AR6" s="15" t="s">
+      <c r="AR6" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="AS6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT6" s="15" t="s">
+      <c r="AS6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT6" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="AU6" s="15" t="s">
+      <c r="AU6" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="AV6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW6" s="15" t="s">
+      <c r="AV6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW6" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="AX6" s="15" t="s">
+      <c r="AX6" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="AY6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ6" s="15" t="s">
+      <c r="AY6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ6" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="BA6" s="15" t="s">
+      <c r="BA6" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="BB6" s="10" t="s">
+      <c r="BB6" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="BC6" s="15" t="s">
+      <c r="BC6" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="BD6" s="15" t="s">
+      <c r="BD6" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="BE6" s="10" t="s">
+      <c r="BE6" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="BF6" s="15" t="s">
+      <c r="BF6" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="BG6" s="15" t="s">
+      <c r="BG6" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BH6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI6" s="15" t="s">
+      <c r="BH6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI6" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BJ6" s="15" t="s">
+      <c r="BJ6" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:62" ht="60" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="15" t="s">
+      <c r="C7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="L7" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M7" s="15" t="s">
+      <c r="L7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N7" s="15" t="s">
+      <c r="N7" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="O7" s="14" t="s">
+      <c r="O7" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P7" s="15" t="s">
+      <c r="P7" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q7" s="15" t="s">
+      <c r="Q7" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S7" s="15" t="s">
+      <c r="R7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="S7" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="T7" s="15" t="s">
+      <c r="T7" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="U7" s="12" t="s">
+      <c r="U7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="15" t="s">
+      <c r="V7" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="W7" s="15" t="s">
+      <c r="W7" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="X7" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y7" s="15" t="s">
+      <c r="X7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y7" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="Z7" s="15" t="s">
+      <c r="Z7" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="AA7" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB7" s="15" t="s">
+      <c r="AA7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB7" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="AC7" s="15" t="s">
+      <c r="AC7" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AD7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE7" s="15" t="s">
+      <c r="AD7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE7" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="AF7" s="15" t="s">
+      <c r="AF7" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="AG7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH7" s="15" t="s">
+      <c r="AG7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH7" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="AI7" s="15" t="s">
+      <c r="AI7" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="AJ7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK7" s="15" t="s">
+      <c r="AJ7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK7" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="AL7" s="15" t="s">
+      <c r="AL7" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="AM7" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN7" s="15" t="s">
+      <c r="AM7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN7" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO7" s="15" t="s">
+      <c r="AO7" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AQ7" s="15" t="s">
+      <c r="AP7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ7" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="AR7" s="15" t="s">
+      <c r="AR7" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="AS7" s="12" t="s">
+      <c r="AS7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AT7" s="15" t="s">
+      <c r="AT7" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="AU7" s="15" t="s">
+      <c r="AU7" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="AV7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW7" s="15" t="s">
+      <c r="AV7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW7" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="AX7" s="15" t="s">
+      <c r="AX7" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="AY7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ7" s="15" t="s">
+      <c r="AY7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ7" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="BA7" s="15" t="s">
+      <c r="BA7" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="BB7" s="12" t="s">
+      <c r="BB7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="BC7" s="15" t="s">
+      <c r="BC7" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="BD7" s="15" t="s">
+      <c r="BD7" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BE7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF7" s="15" t="s">
+      <c r="BE7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF7" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="BG7" s="15" t="s">
+      <c r="BG7" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="BH7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI7" s="15" t="s">
+      <c r="BH7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI7" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BJ7" s="15" t="s">
+      <c r="BJ7" s="13" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="8" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:62" ht="60" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>279</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="15" t="s">
+      <c r="C8" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="L8" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M8" s="15" t="s">
+      <c r="L8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N8" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="O8" s="14" t="s">
+      <c r="O8" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="15" t="s">
+      <c r="P8" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="Q8" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S8" s="15" t="s">
+      <c r="R8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="S8" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="T8" s="15" t="s">
+      <c r="T8" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="U8" s="12" t="s">
+      <c r="U8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="15" t="s">
+      <c r="V8" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="W8" s="15" t="s">
+      <c r="W8" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="X8" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y8" s="15" t="s">
+      <c r="X8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y8" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="Z8" s="15" t="s">
+      <c r="Z8" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="AA8" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB8" s="15" t="s">
+      <c r="AA8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB8" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="AC8" s="15" t="s">
+      <c r="AC8" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AD8" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE8" s="15" t="s">
+      <c r="AD8" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE8" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="AF8" s="15" t="s">
+      <c r="AF8" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="AG8" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH8" s="15" t="s">
+      <c r="AG8" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH8" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="AI8" s="15" t="s">
+      <c r="AI8" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="AJ8" s="14" t="s">
+      <c r="AJ8" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AK8" s="15" t="s">
+      <c r="AK8" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="AL8" s="15" t="s">
+      <c r="AL8" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="AM8" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN8" s="15" t="s">
+      <c r="AM8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN8" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO8" s="15" t="s">
+      <c r="AO8" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP8" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ8" s="15" t="s">
+      <c r="AP8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ8" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="AR8" s="15" t="s">
+      <c r="AR8" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="AS8" s="12" t="s">
+      <c r="AS8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AT8" s="15" t="s">
+      <c r="AT8" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="AU8" s="15" t="s">
+      <c r="AU8" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="AV8" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AW8" s="15" t="s">
+      <c r="AV8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW8" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="AX8" s="15" t="s">
+      <c r="AX8" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="AY8" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ8" s="15" t="s">
+      <c r="AY8" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ8" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="BA8" s="15" t="s">
+      <c r="BA8" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="BB8" s="14" t="s">
+      <c r="BB8" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BC8" s="15" t="s">
+      <c r="BC8" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="BD8" s="15" t="s">
+      <c r="BD8" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="BE8" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF8" s="15" t="s">
+      <c r="BE8" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF8" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="BG8" s="15" t="s">
+      <c r="BG8" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="BH8" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI8" s="15" t="s">
+      <c r="BH8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI8" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BJ8" s="15" t="s">
+      <c r="BJ8" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:62" ht="60" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>311</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="15" t="s">
+      <c r="C9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="15" t="s">
+      <c r="F9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="L9" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M9" s="15" t="s">
+      <c r="L9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N9" s="15" t="s">
+      <c r="N9" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="O9" s="14" t="s">
+      <c r="O9" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P9" s="15" t="s">
+      <c r="P9" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="Q9" s="15" t="s">
+      <c r="Q9" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R9" s="12" t="s">
+      <c r="R9" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="S9" s="15" t="s">
+      <c r="S9" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="T9" s="15" t="s">
+      <c r="T9" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="U9" s="12" t="s">
+      <c r="U9" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="15" t="s">
+      <c r="V9" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="W9" s="15" t="s">
+      <c r="W9" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="X9" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y9" s="15" t="s">
+      <c r="X9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y9" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="Z9" s="15" t="s">
+      <c r="Z9" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="AA9" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB9" s="15" t="s">
+      <c r="AA9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB9" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="AC9" s="15" t="s">
+      <c r="AC9" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AD9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE9" s="15" t="s">
+      <c r="AD9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE9" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="AF9" s="15" t="s">
+      <c r="AF9" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="AG9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH9" s="15" t="s">
+      <c r="AG9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH9" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="AI9" s="15" t="s">
+      <c r="AI9" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="AJ9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK9" s="15" t="s">
+      <c r="AJ9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK9" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="AL9" s="15" t="s">
+      <c r="AL9" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="AM9" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN9" s="15" t="s">
+      <c r="AM9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN9" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO9" s="15" t="s">
+      <c r="AO9" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AQ9" s="15" t="s">
+      <c r="AP9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ9" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="AR9" s="15" t="s">
+      <c r="AR9" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="AS9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT9" s="15" t="s">
+      <c r="AS9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT9" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="AU9" s="15" t="s">
+      <c r="AU9" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="AV9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW9" s="15" t="s">
+      <c r="AV9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW9" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="AX9" s="15" t="s">
+      <c r="AX9" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="AY9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ9" s="15" t="s">
+      <c r="AY9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ9" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="BA9" s="15" t="s">
+      <c r="BA9" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="BB9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC9" s="15" t="s">
+      <c r="BB9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC9" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="BD9" s="15" t="s">
+      <c r="BD9" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="BE9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF9" s="15" t="s">
+      <c r="BE9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF9" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BG9" s="15" t="s">
+      <c r="BG9" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="BH9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI9" s="15" t="s">
+      <c r="BH9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI9" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="BJ9" s="15" t="s">
+      <c r="BJ9" s="13" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="10" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:62" ht="60" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>344</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="15" t="s">
+      <c r="C10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="15" t="s">
+      <c r="F10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="L10" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M10" s="15" t="s">
+      <c r="L10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="N10" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="O10" s="14" t="s">
+      <c r="O10" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P10" s="15" t="s">
+      <c r="P10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q10" s="15" t="s">
+      <c r="Q10" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S10" s="15" t="s">
+      <c r="R10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="S10" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="T10" s="15" t="s">
+      <c r="T10" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="U10" s="12" t="s">
+      <c r="U10" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V10" s="15" t="s">
+      <c r="V10" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="W10" s="15" t="s">
+      <c r="W10" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="X10" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y10" s="15" t="s">
+      <c r="X10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y10" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="Z10" s="15" t="s">
+      <c r="Z10" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="AA10" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB10" s="15" t="s">
+      <c r="AA10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB10" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="AC10" s="15" t="s">
+      <c r="AC10" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="AD10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE10" s="15" t="s">
+      <c r="AD10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE10" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="AF10" s="15" t="s">
+      <c r="AF10" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="AG10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH10" s="15" t="s">
+      <c r="AG10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH10" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="AI10" s="15" t="s">
+      <c r="AI10" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="AJ10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK10" s="15" t="s">
+      <c r="AJ10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK10" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="AL10" s="15" t="s">
+      <c r="AL10" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="AM10" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN10" s="15" t="s">
+      <c r="AM10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN10" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO10" s="15" t="s">
+      <c r="AO10" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AQ10" s="15" t="s">
+      <c r="AP10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ10" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="AR10" s="15" t="s">
+      <c r="AR10" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="AS10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT10" s="15" t="s">
+      <c r="AS10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT10" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="AU10" s="15" t="s">
+      <c r="AU10" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="AV10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW10" s="15" t="s">
+      <c r="AV10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW10" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="AX10" s="15" t="s">
+      <c r="AX10" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="AY10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ10" s="15" t="s">
+      <c r="AY10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ10" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="BA10" s="15" t="s">
+      <c r="BA10" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="BB10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC10" s="15" t="s">
+      <c r="BB10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC10" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="BD10" s="15" t="s">
+      <c r="BD10" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="BE10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF10" s="15" t="s">
+      <c r="BE10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF10" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BG10" s="15" t="s">
+      <c r="BG10" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="BH10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI10" s="15" t="s">
+      <c r="BH10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI10" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="BJ10" s="15" t="s">
+      <c r="BJ10" s="13" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="11" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:62" ht="60" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>378</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="L11" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M11" s="15" t="s">
+      <c r="L11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N11" s="15" t="s">
+      <c r="N11" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="O11" s="14" t="s">
+      <c r="O11" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P11" s="15" t="s">
+      <c r="P11" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q11" s="15" t="s">
+      <c r="Q11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S11" s="15" t="s">
+      <c r="R11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="S11" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="T11" s="15" t="s">
+      <c r="T11" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="U11" s="12" t="s">
+      <c r="U11" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V11" s="15" t="s">
+      <c r="V11" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="W11" s="15" t="s">
+      <c r="W11" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="X11" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y11" s="15" t="s">
+      <c r="X11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y11" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="Z11" s="15" t="s">
+      <c r="Z11" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="AA11" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB11" s="15" t="s">
+      <c r="AA11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB11" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="AC11" s="15" t="s">
+      <c r="AC11" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="AD11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE11" s="15" t="s">
+      <c r="AD11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE11" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="AF11" s="15" t="s">
+      <c r="AF11" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="AG11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH11" s="15" t="s">
+      <c r="AG11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH11" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="AI11" s="15" t="s">
+      <c r="AI11" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="AJ11" s="12" t="s">
+      <c r="AJ11" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AK11" s="15" t="s">
+      <c r="AK11" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="AL11" s="15" t="s">
+      <c r="AL11" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="AM11" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN11" s="15" t="s">
+      <c r="AM11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN11" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO11" s="15" t="s">
+      <c r="AO11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AQ11" s="15" t="s">
+      <c r="AP11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ11" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="AR11" s="15" t="s">
+      <c r="AR11" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="AS11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT11" s="15" t="s">
+      <c r="AS11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT11" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="AU11" s="15" t="s">
+      <c r="AU11" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="AV11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW11" s="15" t="s">
+      <c r="AV11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW11" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="AX11" s="15" t="s">
+      <c r="AX11" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="AY11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ11" s="15" t="s">
+      <c r="AY11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ11" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="BA11" s="15" t="s">
+      <c r="BA11" s="13" t="s">
         <v>404</v>
       </c>
       <c r="BB11" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC11" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC11" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="BD11" s="15" t="s">
+      <c r="BD11" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="BE11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF11" s="15" t="s">
+      <c r="BE11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF11" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BG11" s="15" t="s">
+      <c r="BG11" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="BH11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI11" s="15" t="s">
+      <c r="BH11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI11" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="BJ11" s="15" t="s">
+      <c r="BJ11" s="13" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="12" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:62" ht="60" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>410</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="K12" s="15" t="s">
+      <c r="K12" s="13" t="s">
         <v>417</v>
       </c>
-      <c r="L12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M12" s="15" t="s">
+      <c r="L12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M12" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="N12" s="15" t="s">
+      <c r="N12" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="O12" s="14" t="s">
+      <c r="O12" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P12" s="15" t="s">
+      <c r="P12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q12" s="15" t="s">
+      <c r="Q12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R12" s="12" t="s">
+      <c r="R12" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="S12" s="15" t="s">
+      <c r="S12" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="T12" s="15" t="s">
+      <c r="T12" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="U12" s="12" t="s">
+      <c r="U12" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="15" t="s">
+      <c r="V12" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="W12" s="15" t="s">
+      <c r="W12" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="X12" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y12" s="15" t="s">
+      <c r="X12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y12" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="Z12" s="15" t="s">
+      <c r="Z12" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="AA12" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB12" s="15" t="s">
+      <c r="AA12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB12" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="AC12" s="15" t="s">
+      <c r="AC12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AD12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE12" s="15" t="s">
+      <c r="AD12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE12" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="AF12" s="15" t="s">
+      <c r="AF12" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="AG12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH12" s="15" t="s">
+      <c r="AG12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH12" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="AI12" s="15" t="s">
+      <c r="AI12" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="AJ12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK12" s="15" t="s">
+      <c r="AJ12" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK12" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="AL12" s="15" t="s">
+      <c r="AL12" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="AM12" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN12" s="15" t="s">
+      <c r="AM12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN12" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="AO12" s="15" t="s">
+      <c r="AO12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP12" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ12" s="15" t="s">
+      <c r="AP12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ12" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="AR12" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="AS12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT12" s="15" t="s">
+      <c r="AR12" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="AU12" s="15" t="s">
+      <c r="AS12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT12" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="AV12" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AW12" s="15" t="s">
+      <c r="AU12" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="AX12" s="15" t="s">
+      <c r="AV12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW12" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="AY12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ12" s="15" t="s">
+      <c r="AX12" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="BA12" s="15" t="s">
+      <c r="AY12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ12" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="BB12" s="14" t="s">
+      <c r="BA12" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="BB12" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BC12" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="BD12" s="15" t="s">
+      <c r="BC12" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="BD12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BE12" s="14" t="s">
+      <c r="BE12" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BF12" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="BG12" s="15" t="s">
+      <c r="BF12" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="BG12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BH12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI12" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="BJ12" s="15" t="s">
+      <c r="BH12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI12" s="13" t="s">
         <v>442</v>
       </c>
+      <c r="BJ12" s="13" t="s">
+        <v>443</v>
+      </c>
     </row>
-    <row r="13" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:62" ht="60" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="C13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="15" t="s">
+      <c r="E13" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="F13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="H13" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="I13" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J13" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="K13" s="15" t="s">
+      <c r="J13" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="L13" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M13" s="15" t="s">
+      <c r="K13" s="13" t="s">
         <v>451</v>
       </c>
-      <c r="N13" s="15" t="s">
+      <c r="L13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M13" s="13" t="s">
         <v>452</v>
       </c>
-      <c r="O13" s="14" t="s">
+      <c r="N13" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="O13" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P13" s="15" t="s">
+      <c r="P13" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q13" s="15" t="s">
+      <c r="Q13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S13" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="T13" s="15" t="s">
+      <c r="R13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="S13" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="U13" s="12" t="s">
+      <c r="T13" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="U13" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V13" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="W13" s="15" t="s">
+      <c r="V13" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="X13" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y13" s="15" t="s">
+      <c r="W13" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="Z13" s="15" t="s">
+      <c r="X13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y13" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="AA13" s="14" t="s">
+      <c r="Z13" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="AA13" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AB13" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="AC13" s="15" t="s">
+      <c r="AB13" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="AD13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE13" s="15" t="s">
+      <c r="AC13" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="AF13" s="15" t="s">
+      <c r="AD13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE13" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="AG13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH13" s="15" t="s">
+      <c r="AF13" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="AI13" s="15" t="s">
+      <c r="AG13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH13" s="13" t="s">
         <v>464</v>
       </c>
-      <c r="AJ13" s="14" t="s">
+      <c r="AI13" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="AJ13" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AK13" s="15" t="s">
-        <v>465</v>
-      </c>
-      <c r="AL13" s="15" t="s">
+      <c r="AK13" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="AM13" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN13" s="15" t="s">
+      <c r="AL13" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="AM13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN13" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO13" s="15" t="s">
+      <c r="AO13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP13" s="14" t="s">
+      <c r="AP13" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AQ13" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="AR13" s="15" t="s">
+      <c r="AQ13" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="AS13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT13" s="15" t="s">
+      <c r="AR13" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="AU13" s="15" t="s">
+      <c r="AS13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT13" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="AV13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW13" s="15" t="s">
+      <c r="AU13" s="13" t="s">
         <v>471</v>
       </c>
-      <c r="AX13" s="15" t="s">
+      <c r="AV13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW13" s="13" t="s">
         <v>472</v>
       </c>
-      <c r="AY13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ13" s="15" t="s">
+      <c r="AX13" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="BA13" s="15" t="s">
+      <c r="AY13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ13" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="BB13" s="12" t="s">
+      <c r="BA13" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="BB13" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="BC13" s="15" t="s">
-        <v>475</v>
-      </c>
-      <c r="BD13" s="15" t="s">
+      <c r="BC13" s="13" t="s">
         <v>476</v>
       </c>
-      <c r="BE13" s="14" t="s">
+      <c r="BD13" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="BE13" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BF13" s="15" t="s">
+      <c r="BF13" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="BG13" s="15" t="s">
+      <c r="BG13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BH13" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI13" s="15" t="s">
+      <c r="BH13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI13" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BJ13" s="15" t="s">
+      <c r="BJ13" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:62" ht="60" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="C14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="15" t="s">
+      <c r="E14" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="15" t="s">
-        <v>481</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="H14" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="K14" s="15" t="s">
+      <c r="J14" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M14" s="15" t="s">
+      <c r="K14" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="N14" s="15" t="s">
+      <c r="L14" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="O14" s="14" t="s">
+      <c r="N14" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="O14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P14" s="15" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q14" s="15" t="s">
+      <c r="P14" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S14" s="15" t="s">
-        <v>487</v>
-      </c>
-      <c r="T14" s="15" t="s">
+      <c r="R14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="S14" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="U14" s="12" t="s">
+      <c r="T14" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="U14" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="W14" s="15" t="s">
+      <c r="V14" s="13" t="s">
         <v>490</v>
       </c>
-      <c r="X14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y14" s="15" t="s">
+      <c r="W14" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="Z14" s="15" t="s">
-        <v>483</v>
-      </c>
-      <c r="AA14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB14" s="15" t="s">
+      <c r="X14" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y14" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="AC14" s="15" t="s">
+      <c r="Z14" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB14" s="13" t="s">
         <v>493</v>
       </c>
-      <c r="AD14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE14" s="15" t="s">
+      <c r="AC14" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="AF14" s="15" t="s">
+      <c r="AD14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE14" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="AG14" s="12" t="s">
+      <c r="AF14" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="AG14" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AH14" s="15" t="s">
-        <v>496</v>
-      </c>
-      <c r="AI14" s="15" t="s">
+      <c r="AH14" s="13" t="s">
         <v>497</v>
       </c>
-      <c r="AJ14" s="14" t="s">
+      <c r="AI14" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="AJ14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AK14" s="15" t="s">
-        <v>498</v>
-      </c>
-      <c r="AL14" s="15" t="s">
+      <c r="AK14" s="13" t="s">
         <v>499</v>
       </c>
-      <c r="AM14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN14" s="15" t="s">
+      <c r="AL14" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="AO14" s="15" t="s">
+      <c r="AM14" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN14" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="AO14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP14" s="14" t="s">
+      <c r="AP14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AQ14" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="AR14" s="15" t="s">
+      <c r="AQ14" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="AS14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT14" s="15" t="s">
+      <c r="AR14" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="AU14" s="15" t="s">
+      <c r="AS14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT14" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="AV14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW14" s="15" t="s">
+      <c r="AU14" s="13" t="s">
         <v>505</v>
       </c>
-      <c r="AX14" s="15" t="s">
+      <c r="AV14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW14" s="13" t="s">
         <v>506</v>
       </c>
-      <c r="AY14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ14" s="15" t="s">
+      <c r="AX14" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="BA14" s="15" t="s">
+      <c r="AY14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ14" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="BB14" s="14" t="s">
+      <c r="BA14" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="BB14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BC14" s="15" t="s">
-        <v>509</v>
-      </c>
-      <c r="BD14" s="15" t="s">
+      <c r="BC14" s="13" t="s">
         <v>510</v>
       </c>
-      <c r="BE14" s="14" t="s">
+      <c r="BD14" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="BE14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BF14" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="BG14" s="15" t="s">
+      <c r="BF14" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="BG14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BH14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI14" s="15" t="s">
+      <c r="BH14" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BJ14" s="15" t="s">
+      <c r="BJ14" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:62" ht="60" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="15" t="s">
         <v>514</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="C15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" s="15" t="s">
+      <c r="E15" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="F15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="I15" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" s="15" t="s">
+      <c r="H15" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="K15" s="15" t="s">
+      <c r="I15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="L15" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M15" s="15" t="s">
+      <c r="K15" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="N15" s="15" t="s">
+      <c r="L15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="13" t="s">
         <v>521</v>
       </c>
-      <c r="O15" s="14" t="s">
+      <c r="N15" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="O15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P15" s="15" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q15" s="15" t="s">
+      <c r="P15" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="R15" s="12" t="s">
+      <c r="Q15" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="R15" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="S15" s="15" t="s">
-        <v>524</v>
-      </c>
-      <c r="T15" s="15" t="s">
+      <c r="S15" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="U15" s="12" t="s">
+      <c r="T15" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="U15" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V15" s="15" t="s">
-        <v>526</v>
-      </c>
-      <c r="W15" s="15" t="s">
+      <c r="V15" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="X15" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y15" s="15" t="s">
+      <c r="W15" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="Z15" s="15" t="s">
+      <c r="X15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y15" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="AA15" s="14" t="s">
+      <c r="Z15" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="AA15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AB15" s="15" t="s">
-        <v>530</v>
-      </c>
-      <c r="AC15" s="15" t="s">
+      <c r="AB15" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="AD15" s="14" t="s">
+      <c r="AC15" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="AD15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AE15" s="15" t="s">
-        <v>532</v>
-      </c>
-      <c r="AF15" s="15" t="s">
+      <c r="AE15" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="AG15" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH15" s="15" t="s">
+      <c r="AF15" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="AI15" s="15" t="s">
+      <c r="AG15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH15" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="AJ15" s="14" t="s">
+      <c r="AI15" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="AJ15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AK15" s="15" t="s">
+      <c r="AK15" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="AL15" s="15" t="s">
+      <c r="AL15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AM15" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN15" s="15" t="s">
+      <c r="AM15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN15" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO15" s="15" t="s">
+      <c r="AO15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP15" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ15" s="15" t="s">
-        <v>536</v>
-      </c>
-      <c r="AR15" s="15" t="s">
+      <c r="AP15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ15" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="AR15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AS15" s="12" t="s">
+      <c r="AS15" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AT15" s="15" t="s">
-        <v>537</v>
-      </c>
-      <c r="AU15" s="15" t="s">
+      <c r="AT15" s="13" t="s">
         <v>538</v>
       </c>
-      <c r="AV15" s="14" t="s">
+      <c r="AU15" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="AV15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AW15" s="15" t="s">
-        <v>539</v>
-      </c>
-      <c r="AX15" s="15" t="s">
+      <c r="AW15" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="AY15" s="14" t="s">
+      <c r="AX15" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="AY15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AZ15" s="15" t="s">
-        <v>541</v>
-      </c>
-      <c r="BA15" s="15" t="s">
+      <c r="AZ15" s="13" t="s">
         <v>542</v>
       </c>
-      <c r="BB15" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC15" s="15" t="s">
+      <c r="BA15" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="BD15" s="15" t="s">
+      <c r="BB15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC15" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="BE15" s="14" t="s">
+      <c r="BD15" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="BE15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BF15" s="15" t="s">
+      <c r="BF15" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="BG15" s="15" t="s">
+      <c r="BG15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BH15" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI15" s="15" t="s">
+      <c r="BH15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI15" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="BJ15" s="15" t="s">
-        <v>545</v>
+      <c r="BJ15" s="13" t="s">
+        <v>546</v>
       </c>
     </row>
-    <row r="16" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:62" ht="60" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>548</v>
-      </c>
-      <c r="F16" s="12" t="s">
+      <c r="E16" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>549</v>
-      </c>
-      <c r="H16" s="15" t="s">
+      <c r="G16" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="H16" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="I16" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="K16" s="15" t="s">
-        <v>551</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M16" s="15" t="s">
+      <c r="K16" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N16" s="15" t="s">
-        <v>552</v>
-      </c>
-      <c r="O16" s="14" t="s">
+      <c r="N16" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="O16" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P16" s="15" t="s">
+      <c r="P16" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q16" s="15" t="s">
+      <c r="Q16" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S16" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="T16" s="15" t="s">
+      <c r="R16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" s="13" t="s">
         <v>554</v>
       </c>
-      <c r="U16" s="12" t="s">
+      <c r="T16" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="U16" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V16" s="15" t="s">
-        <v>555</v>
-      </c>
-      <c r="W16" s="15" t="s">
+      <c r="V16" s="13" t="s">
         <v>556</v>
       </c>
-      <c r="X16" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y16" s="15" t="s">
+      <c r="W16" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y16" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="Z16" s="15" t="s">
-        <v>557</v>
-      </c>
-      <c r="AA16" s="14" t="s">
+      <c r="Z16" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="AA16" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AB16" s="15" t="s">
-        <v>558</v>
-      </c>
-      <c r="AC16" s="15" t="s">
+      <c r="AB16" s="13" t="s">
         <v>559</v>
       </c>
-      <c r="AD16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE16" s="15" t="s">
+      <c r="AC16" s="13" t="s">
         <v>560</v>
       </c>
-      <c r="AF16" s="15" t="s">
+      <c r="AD16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE16" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="AG16" s="12" t="s">
+      <c r="AF16" s="13" t="s">
+        <v>562</v>
+      </c>
+      <c r="AG16" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AH16" s="15" t="s">
-        <v>562</v>
-      </c>
-      <c r="AI16" s="15" t="s">
+      <c r="AH16" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="AJ16" s="14" t="s">
+      <c r="AI16" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="AJ16" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="AK16" s="15" t="s">
+      <c r="AK16" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="AL16" s="15" t="s">
+      <c r="AL16" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AM16" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN16" s="15" t="s">
+      <c r="AM16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN16" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AO16" s="15" t="s">
+      <c r="AO16" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AP16" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ16" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="AR16" s="15" t="s">
+      <c r="AP16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ16" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="AR16" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AS16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT16" s="15" t="s">
+      <c r="AS16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT16" s="13" t="s">
+        <v>566</v>
+      </c>
+      <c r="AU16" s="13" t="s">
+        <v>567</v>
+      </c>
+      <c r="AV16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW16" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="AX16" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="AY16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ16" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="BA16" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="BB16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC16" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="BD16" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="BE16" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF16" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="BG16" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI16" s="13" t="s">
+        <v>573</v>
+      </c>
+      <c r="BJ16" s="13" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="17" spans="1:62" ht="60" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>579</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>580</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>581</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>582</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>583</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>582</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="R17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="S17" s="13" t="s">
+        <v>584</v>
+      </c>
+      <c r="T17" s="13" t="s">
+        <v>585</v>
+      </c>
+      <c r="U17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V17" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="W17" s="13" t="s">
+        <v>587</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y17" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="Z17" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="AA17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB17" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="AC17" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="AD17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE17" s="13" t="s">
+        <v>592</v>
+      </c>
+      <c r="AF17" s="13" t="s">
+        <v>593</v>
+      </c>
+      <c r="AG17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH17" s="13" t="s">
+        <v>594</v>
+      </c>
+      <c r="AI17" s="13" t="s">
+        <v>595</v>
+      </c>
+      <c r="AJ17" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK17" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="AL17" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN17" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO17" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ17" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="AR17" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT17" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="AU17" s="13" t="s">
+        <v>598</v>
+      </c>
+      <c r="AV17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW17" s="13" t="s">
+        <v>599</v>
+      </c>
+      <c r="AX17" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="AY17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ17" s="13" t="s">
+        <v>600</v>
+      </c>
+      <c r="BA17" s="13" t="s">
+        <v>601</v>
+      </c>
+      <c r="BB17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC17" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="BD17" s="13" t="s">
+        <v>602</v>
+      </c>
+      <c r="BE17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF17" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="BG17" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="BH17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI17" s="13" t="s">
+        <v>604</v>
+      </c>
+      <c r="BJ17" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:62" ht="60" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>610</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>612</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>613</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>612</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="S18" s="13" t="s">
+        <v>614</v>
+      </c>
+      <c r="T18" s="13" t="s">
+        <v>615</v>
+      </c>
+      <c r="U18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V18" s="13" t="s">
+        <v>616</v>
+      </c>
+      <c r="W18" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="X18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y18" s="13" t="s">
+        <v>618</v>
+      </c>
+      <c r="Z18" s="13" t="s">
+        <v>619</v>
+      </c>
+      <c r="AA18" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB18" s="13" t="s">
+        <v>620</v>
+      </c>
+      <c r="AC18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE18" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="AF18" s="13" t="s">
+        <v>622</v>
+      </c>
+      <c r="AG18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH18" s="13" t="s">
+        <v>623</v>
+      </c>
+      <c r="AI18" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="AJ18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK18" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="AL18" s="13" t="s">
+        <v>626</v>
+      </c>
+      <c r="AM18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN18" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="AO18" s="13" t="s">
+        <v>626</v>
+      </c>
+      <c r="AP18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ18" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="AR18" s="13" t="s">
+        <v>626</v>
+      </c>
+      <c r="AS18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT18" s="13" t="s">
+        <v>629</v>
+      </c>
+      <c r="AU18" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="AV18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW18" s="13" t="s">
+        <v>631</v>
+      </c>
+      <c r="AX18" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="AY18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ18" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="BA18" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="BB18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC18" s="13" t="s">
+        <v>635</v>
+      </c>
+      <c r="BD18" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="BE18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF18" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="BG18" s="13" t="s">
+        <v>637</v>
+      </c>
+      <c r="BH18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI18" s="13" t="s">
+        <v>638</v>
+      </c>
+      <c r="BJ18" s="13" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="19" spans="1:62" ht="60" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>645</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>646</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>647</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="S19" s="13" t="s">
+        <v>648</v>
+      </c>
+      <c r="T19" s="13" t="s">
+        <v>649</v>
+      </c>
+      <c r="U19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V19" s="13" t="s">
+        <v>650</v>
+      </c>
+      <c r="W19" s="13" t="s">
+        <v>651</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y19" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z19" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="AA19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB19" s="13" t="s">
+        <v>653</v>
+      </c>
+      <c r="AC19" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE19" s="13" t="s">
+        <v>654</v>
+      </c>
+      <c r="AF19" s="13" t="s">
+        <v>655</v>
+      </c>
+      <c r="AG19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH19" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="AI19" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="AJ19" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK19" s="13" t="s">
+        <v>658</v>
+      </c>
+      <c r="AL19" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="AM19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN19" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO19" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ19" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="AR19" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="AS19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT19" s="13" t="s">
+        <v>662</v>
+      </c>
+      <c r="AU19" s="13" t="s">
+        <v>663</v>
+      </c>
+      <c r="AV19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW19" s="13" t="s">
+        <v>664</v>
+      </c>
+      <c r="AX19" s="13" t="s">
+        <v>665</v>
+      </c>
+      <c r="AY19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ19" s="13" t="s">
+        <v>666</v>
+      </c>
+      <c r="BA19" s="13" t="s">
+        <v>667</v>
+      </c>
+      <c r="BB19" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC19" s="13" t="s">
+        <v>668</v>
+      </c>
+      <c r="BD19" s="13" t="s">
+        <v>669</v>
+      </c>
+      <c r="BE19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF19" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="BG19" s="13" t="s">
+        <v>670</v>
+      </c>
+      <c r="BH19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI19" s="13" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ19" s="13" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="20" spans="1:62" ht="60" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>675</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>676</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>678</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>679</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>680</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="P20" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="S20" s="13" t="s">
+        <v>681</v>
+      </c>
+      <c r="T20" s="13" t="s">
+        <v>682</v>
+      </c>
+      <c r="U20" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V20" s="13" t="s">
+        <v>683</v>
+      </c>
+      <c r="W20" s="13" t="s">
+        <v>684</v>
+      </c>
+      <c r="X20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y20" s="13" t="s">
+        <v>685</v>
+      </c>
+      <c r="Z20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB20" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE20" s="13" t="s">
+        <v>686</v>
+      </c>
+      <c r="AF20" s="13" t="s">
+        <v>687</v>
+      </c>
+      <c r="AG20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH20" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="AI20" s="13" t="s">
+        <v>688</v>
+      </c>
+      <c r="AJ20" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK20" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="AL20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN20" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ20" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="AU16" s="15" t="s">
-        <v>566</v>
-      </c>
-      <c r="AV16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW16" s="15" t="s">
-        <v>567</v>
-      </c>
-      <c r="AX16" s="15" t="s">
-        <v>568</v>
-      </c>
-      <c r="AY16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ16" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="BA16" s="15" t="s">
-        <v>570</v>
-      </c>
-      <c r="BB16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC16" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="BD16" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="BE16" s="14" t="s">
+      <c r="AR20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT20" s="13" t="s">
+        <v>689</v>
+      </c>
+      <c r="AU20" s="13" t="s">
+        <v>690</v>
+      </c>
+      <c r="AV20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW20" s="13" t="s">
+        <v>691</v>
+      </c>
+      <c r="AX20" s="13" t="s">
+        <v>680</v>
+      </c>
+      <c r="AY20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ20" s="13" t="s">
+        <v>692</v>
+      </c>
+      <c r="BA20" s="13" t="s">
+        <v>693</v>
+      </c>
+      <c r="BB20" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC20" s="13" t="s">
+        <v>694</v>
+      </c>
+      <c r="BD20" s="13" t="s">
+        <v>695</v>
+      </c>
+      <c r="BE20" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BF16" s="15" t="s">
+      <c r="BF20" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="BG16" s="15" t="s">
+      <c r="BG20" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BH16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI16" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="BJ16" s="15" t="s">
-        <v>573</v>
+      <c r="BH20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI20" s="13" t="s">
+        <v>604</v>
+      </c>
+      <c r="BJ20" s="13" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>576</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="F17" s="12" t="s">
+    <row r="21" spans="1:62" ht="60" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="F21" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="15" t="s">
-        <v>578</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>579</v>
-      </c>
-      <c r="I17" s="12" t="s">
+      <c r="G21" s="13" t="s">
+        <v>700</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I21" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>581</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M17" s="15" t="s">
-        <v>582</v>
-      </c>
-      <c r="N17" s="15" t="s">
-        <v>581</v>
-      </c>
-      <c r="O17" s="14" t="s">
+      <c r="J21" s="13" t="s">
+        <v>702</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>703</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>703</v>
+      </c>
+      <c r="O21" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P17" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q17" s="15" t="s">
+      <c r="P21" s="13" t="s">
+        <v>705</v>
+      </c>
+      <c r="Q21" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R17" s="12" t="s">
+      <c r="R21" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="S17" s="15" t="s">
-        <v>583</v>
-      </c>
-      <c r="T17" s="15" t="s">
-        <v>584</v>
-      </c>
-      <c r="U17" s="12" t="s">
+      <c r="S21" s="13" t="s">
+        <v>706</v>
+      </c>
+      <c r="T21" s="13" t="s">
+        <v>707</v>
+      </c>
+      <c r="U21" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="V21" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="W21" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y21" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z21" s="13" t="s">
+        <v>703</v>
+      </c>
+      <c r="AA21" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB21" s="13" t="s">
+        <v>710</v>
+      </c>
+      <c r="AC21" s="13" t="s">
+        <v>711</v>
+      </c>
+      <c r="AD21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE21" s="13" t="s">
+        <v>712</v>
+      </c>
+      <c r="AF21" s="13" t="s">
+        <v>713</v>
+      </c>
+      <c r="AG21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH21" s="13" t="s">
+        <v>714</v>
+      </c>
+      <c r="AI21" s="13" t="s">
+        <v>715</v>
+      </c>
+      <c r="AJ21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK21" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="AL21" s="13" t="s">
+        <v>717</v>
+      </c>
+      <c r="AM21" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN21" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO21" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ21" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="AR21" s="13" t="s">
+        <v>717</v>
+      </c>
+      <c r="AS21" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="V17" s="15" t="s">
-        <v>585</v>
-      </c>
-      <c r="W17" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="X17" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y17" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="Z17" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="AA17" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB17" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="AC17" s="15" t="s">
-        <v>590</v>
-      </c>
-      <c r="AD17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE17" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="AF17" s="15" t="s">
-        <v>592</v>
-      </c>
-      <c r="AG17" s="12" t="s">
+      <c r="AT21" s="13" t="s">
+        <v>719</v>
+      </c>
+      <c r="AU21" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="AV21" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW21" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="AX21" s="13" t="s">
+        <v>722</v>
+      </c>
+      <c r="AY21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ21" s="13" t="s">
+        <v>723</v>
+      </c>
+      <c r="BA21" s="13" t="s">
+        <v>724</v>
+      </c>
+      <c r="BB21" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AH17" s="15" t="s">
-        <v>593</v>
-      </c>
-      <c r="AI17" s="15" t="s">
-        <v>594</v>
-      </c>
-      <c r="AJ17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK17" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="AL17" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AM17" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN17" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO17" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AP17" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ17" s="15" t="s">
-        <v>595</v>
-      </c>
-      <c r="AR17" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AS17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT17" s="15" t="s">
-        <v>596</v>
-      </c>
-      <c r="AU17" s="15" t="s">
-        <v>597</v>
-      </c>
-      <c r="AV17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW17" s="15" t="s">
-        <v>598</v>
-      </c>
-      <c r="AX17" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="AY17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ17" s="15" t="s">
-        <v>599</v>
-      </c>
-      <c r="BA17" s="15" t="s">
-        <v>600</v>
-      </c>
-      <c r="BB17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC17" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="BD17" s="15" t="s">
-        <v>601</v>
-      </c>
-      <c r="BE17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF17" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="BG17" s="15" t="s">
-        <v>602</v>
-      </c>
-      <c r="BH17" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI17" s="15" t="s">
-        <v>603</v>
-      </c>
-      <c r="BJ17" s="15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>606</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>607</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>608</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>609</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>610</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>611</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M18" s="15" t="s">
-        <v>612</v>
-      </c>
-      <c r="N18" s="15" t="s">
-        <v>611</v>
-      </c>
-      <c r="O18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="P18" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="R18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S18" s="15" t="s">
-        <v>613</v>
-      </c>
-      <c r="T18" s="15" t="s">
-        <v>614</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="V18" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="W18" s="15" t="s">
-        <v>616</v>
-      </c>
-      <c r="X18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y18" s="15" t="s">
-        <v>617</v>
-      </c>
-      <c r="Z18" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="AA18" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB18" s="15" t="s">
-        <v>619</v>
-      </c>
-      <c r="AC18" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE18" s="15" t="s">
-        <v>620</v>
-      </c>
-      <c r="AF18" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="AG18" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH18" s="15" t="s">
-        <v>622</v>
-      </c>
-      <c r="AI18" s="15" t="s">
-        <v>623</v>
-      </c>
-      <c r="AJ18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK18" s="15" t="s">
-        <v>624</v>
-      </c>
-      <c r="AL18" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="AM18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN18" s="15" t="s">
-        <v>626</v>
-      </c>
-      <c r="AO18" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="AP18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AQ18" s="15" t="s">
-        <v>627</v>
-      </c>
-      <c r="AR18" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="AS18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT18" s="15" t="s">
-        <v>628</v>
-      </c>
-      <c r="AU18" s="15" t="s">
-        <v>629</v>
-      </c>
-      <c r="AV18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW18" s="15" t="s">
-        <v>630</v>
-      </c>
-      <c r="AX18" s="15" t="s">
-        <v>631</v>
-      </c>
-      <c r="AY18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ18" s="15" t="s">
-        <v>632</v>
-      </c>
-      <c r="BA18" s="15" t="s">
-        <v>633</v>
-      </c>
-      <c r="BB18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC18" s="15" t="s">
-        <v>634</v>
-      </c>
-      <c r="BD18" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="BE18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF18" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="BG18" s="15" t="s">
-        <v>636</v>
-      </c>
-      <c r="BH18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI18" s="15" t="s">
-        <v>637</v>
-      </c>
-      <c r="BJ18" s="15" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="19" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>641</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>642</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>643</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>644</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="J19" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>645</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M19" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="N19" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="O19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="P19" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="R19" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="S19" s="15" t="s">
-        <v>647</v>
-      </c>
-      <c r="T19" s="15" t="s">
-        <v>648</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="V19" s="15" t="s">
-        <v>649</v>
-      </c>
-      <c r="W19" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="X19" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y19" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z19" s="15" t="s">
-        <v>651</v>
-      </c>
-      <c r="AA19" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB19" s="15" t="s">
-        <v>652</v>
-      </c>
-      <c r="AC19" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE19" s="15" t="s">
-        <v>653</v>
-      </c>
-      <c r="AF19" s="15" t="s">
-        <v>654</v>
-      </c>
-      <c r="AG19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH19" s="15" t="s">
-        <v>655</v>
-      </c>
-      <c r="AI19" s="15" t="s">
-        <v>656</v>
-      </c>
-      <c r="AJ19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK19" s="15" t="s">
-        <v>657</v>
-      </c>
-      <c r="AL19" s="15" t="s">
-        <v>658</v>
-      </c>
-      <c r="AM19" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN19" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO19" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AP19" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ19" s="15" t="s">
-        <v>659</v>
-      </c>
-      <c r="AR19" s="15" t="s">
-        <v>660</v>
-      </c>
-      <c r="AS19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT19" s="15" t="s">
-        <v>661</v>
-      </c>
-      <c r="AU19" s="15" t="s">
-        <v>662</v>
-      </c>
-      <c r="AV19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW19" s="15" t="s">
-        <v>663</v>
-      </c>
-      <c r="AX19" s="15" t="s">
-        <v>664</v>
-      </c>
-      <c r="AY19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ19" s="15" t="s">
-        <v>665</v>
-      </c>
-      <c r="BA19" s="15" t="s">
-        <v>666</v>
-      </c>
-      <c r="BB19" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC19" s="15" t="s">
-        <v>667</v>
-      </c>
-      <c r="BD19" s="15" t="s">
-        <v>668</v>
-      </c>
-      <c r="BE19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF19" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="BG19" s="15" t="s">
-        <v>669</v>
-      </c>
-      <c r="BH19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI19" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="BJ19" s="15" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="20" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>674</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>675</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>676</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>677</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>678</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>679</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M20" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="N20" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="O20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="P20" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="R20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S20" s="15" t="s">
-        <v>680</v>
-      </c>
-      <c r="T20" s="15" t="s">
-        <v>681</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="V20" s="15" t="s">
-        <v>682</v>
-      </c>
-      <c r="W20" s="15" t="s">
-        <v>683</v>
-      </c>
-      <c r="X20" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y20" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="Z20" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA20" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB20" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="AC20" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE20" s="15" t="s">
-        <v>685</v>
-      </c>
-      <c r="AF20" s="15" t="s">
-        <v>686</v>
-      </c>
-      <c r="AG20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH20" s="15" t="s">
-        <v>463</v>
-      </c>
-      <c r="AI20" s="15" t="s">
-        <v>687</v>
-      </c>
-      <c r="AJ20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK20" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="AL20" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AM20" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN20" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO20" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AP20" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ20" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="AR20" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AS20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT20" s="15" t="s">
-        <v>688</v>
-      </c>
-      <c r="AU20" s="15" t="s">
-        <v>689</v>
-      </c>
-      <c r="AV20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW20" s="15" t="s">
-        <v>690</v>
-      </c>
-      <c r="AX20" s="15" t="s">
-        <v>679</v>
-      </c>
-      <c r="AY20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ20" s="15" t="s">
-        <v>691</v>
-      </c>
-      <c r="BA20" s="15" t="s">
-        <v>692</v>
-      </c>
-      <c r="BB20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC20" s="15" t="s">
-        <v>693</v>
-      </c>
-      <c r="BD20" s="15" t="s">
-        <v>694</v>
-      </c>
-      <c r="BE20" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF20" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="BG20" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BH20" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI20" s="15" t="s">
-        <v>603</v>
-      </c>
-      <c r="BJ20" s="15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:62" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>697</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>698</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>699</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>700</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>701</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>702</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M21" s="15" t="s">
-        <v>703</v>
-      </c>
-      <c r="N21" s="15" t="s">
-        <v>702</v>
-      </c>
-      <c r="O21" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="P21" s="15" t="s">
-        <v>704</v>
-      </c>
-      <c r="Q21" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="R21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="S21" s="15" t="s">
-        <v>705</v>
-      </c>
-      <c r="T21" s="15" t="s">
-        <v>706</v>
-      </c>
-      <c r="U21" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="V21" s="15" t="s">
-        <v>707</v>
-      </c>
-      <c r="W21" s="15" t="s">
-        <v>708</v>
-      </c>
-      <c r="X21" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y21" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z21" s="15" t="s">
-        <v>702</v>
-      </c>
-      <c r="AA21" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB21" s="15" t="s">
-        <v>709</v>
-      </c>
-      <c r="AC21" s="15" t="s">
-        <v>710</v>
-      </c>
-      <c r="AD21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE21" s="15" t="s">
-        <v>711</v>
-      </c>
-      <c r="AF21" s="15" t="s">
-        <v>712</v>
-      </c>
-      <c r="AG21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH21" s="15" t="s">
-        <v>713</v>
-      </c>
-      <c r="AI21" s="15" t="s">
-        <v>714</v>
-      </c>
-      <c r="AJ21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK21" s="15" t="s">
-        <v>715</v>
-      </c>
-      <c r="AL21" s="15" t="s">
-        <v>716</v>
-      </c>
-      <c r="AM21" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN21" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="AO21" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AP21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AQ21" s="15" t="s">
-        <v>717</v>
-      </c>
-      <c r="AR21" s="15" t="s">
-        <v>716</v>
-      </c>
-      <c r="AS21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT21" s="15" t="s">
-        <v>718</v>
-      </c>
-      <c r="AU21" s="15" t="s">
-        <v>719</v>
-      </c>
-      <c r="AV21" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AW21" s="15" t="s">
-        <v>720</v>
-      </c>
-      <c r="AX21" s="15" t="s">
-        <v>721</v>
-      </c>
-      <c r="AY21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ21" s="15" t="s">
-        <v>722</v>
-      </c>
-      <c r="BA21" s="15" t="s">
-        <v>723</v>
-      </c>
-      <c r="BB21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC21" s="15" t="s">
-        <v>724</v>
-      </c>
-      <c r="BD21" s="15" t="s">
+      <c r="BC21" s="13" t="s">
         <v>725</v>
       </c>
-      <c r="BE21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF21" s="15" t="s">
+      <c r="BD21" s="13" t="s">
+        <v>726</v>
+      </c>
+      <c r="BE21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF21" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BG21" s="15" t="s">
-        <v>726</v>
-      </c>
-      <c r="BH21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI21" s="15" t="s">
+      <c r="BG21" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="BJ21" s="15" t="s">
+      <c r="BH21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI21" s="13" t="s">
         <v>728</v>
+      </c>
+      <c r="BJ21" s="13" t="s">
+        <v>729</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -7462,590 +7512,590 @@
     <col min="10" max="10" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>729</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>730</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="14" t="s">
         <v>731</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="14" t="s">
         <v>732</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="D1" s="14" t="s">
+        <v>733</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>733</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="H1" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="14" t="s">
         <v>734</v>
       </c>
+      <c r="J1" s="14" t="s">
+        <v>735</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:10" ht="120" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="15" t="s">
         <v>736</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="15" t="s">
         <v>737</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="15" t="s">
         <v>738</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="15" t="s">
         <v>739</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6" t="s">
+      <c r="F2" s="15"/>
+      <c r="G2" s="15" t="s">
         <v>740</v>
       </c>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15" t="s">
+        <v>741</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:10" ht="120" customHeight="1">
+      <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="15" t="s">
         <v>742</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="15" t="s">
         <v>743</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="15" t="s">
         <v>744</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="15" t="s">
         <v>745</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="15" t="s">
         <v>746</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6" t="s">
+      <c r="G3" s="15" t="s">
         <v>747</v>
       </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15" t="s">
+        <v>748</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:10" ht="120" customHeight="1">
+      <c r="A4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>748</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="15" t="s">
         <v>749</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="C4" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="D4" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>751</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="F4" s="15" t="s">
         <v>752</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6" t="s">
+      <c r="G4" s="15" t="s">
         <v>753</v>
       </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15" t="s">
+        <v>754</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:10" ht="120" customHeight="1">
+      <c r="A5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>754</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="15" t="s">
         <v>755</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="15" t="s">
         <v>756</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="15" t="s">
         <v>757</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6" t="s">
+      <c r="E5" s="15" t="s">
         <v>758</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
         <v>759</v>
       </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6" t="s">
+      <c r="H5" s="15" t="s">
         <v>760</v>
       </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15" t="s">
+        <v>761</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:10" ht="120" customHeight="1">
+      <c r="A6" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>761</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>762</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="C6" s="15" t="s">
         <v>763</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="D6" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>764</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="15" t="s">
         <v>765</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6" t="s">
+      <c r="G6" s="15" t="s">
         <v>766</v>
       </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15" t="s">
+        <v>767</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:10" ht="120" customHeight="1">
+      <c r="A7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>767</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="15" t="s">
         <v>768</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="C7" s="15" t="s">
         <v>769</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="D7" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>770</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="15" t="s">
         <v>771</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6" t="s">
+      <c r="G7" s="15" t="s">
         <v>772</v>
       </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15" t="s">
+        <v>773</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:10" ht="120" customHeight="1">
+      <c r="A8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>773</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="15" t="s">
         <v>774</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="C8" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="D8" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="15" t="s">
         <v>777</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6" t="s">
+      <c r="G8" s="15" t="s">
         <v>778</v>
       </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15" t="s">
+        <v>779</v>
+      </c>
     </row>
-    <row r="9" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:10" ht="120" customHeight="1">
+      <c r="A9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="15" t="s">
         <v>780</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>756</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="C9" s="15" t="s">
         <v>781</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="s">
+      <c r="D9" s="15" t="s">
+        <v>757</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>782</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="F9" s="15"/>
+      <c r="G9" s="15" t="s">
         <v>783</v>
       </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6" t="s">
+      <c r="H9" s="15" t="s">
         <v>784</v>
       </c>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15" t="s">
+        <v>785</v>
+      </c>
     </row>
-    <row r="10" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:10" ht="120" customHeight="1">
+      <c r="A10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>786</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>756</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="C10" s="15" t="s">
         <v>787</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="s">
+      <c r="D10" s="15" t="s">
+        <v>757</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>788</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="F10" s="15"/>
+      <c r="G10" s="15" t="s">
         <v>789</v>
       </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6" t="s">
+      <c r="H10" s="15" t="s">
         <v>790</v>
       </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15" t="s">
+        <v>791</v>
+      </c>
     </row>
-    <row r="11" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:10" ht="120" customHeight="1">
+      <c r="A11" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="15" t="s">
         <v>792</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>756</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="C11" s="15" t="s">
         <v>793</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
+      <c r="D11" s="15" t="s">
+        <v>757</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>794</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="F11" s="15"/>
+      <c r="G11" s="15" t="s">
         <v>795</v>
       </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6" t="s">
+      <c r="H11" s="15" t="s">
         <v>796</v>
       </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15" t="s">
+        <v>797</v>
+      </c>
     </row>
-    <row r="12" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:10" ht="120" customHeight="1">
+      <c r="A12" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>797</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="15" t="s">
         <v>798</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="C12" s="15" t="s">
         <v>799</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="D12" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>800</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="F12" s="15" t="s">
         <v>801</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="G12" s="15" t="s">
+        <v>802</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
     </row>
-    <row r="13" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:10" ht="120" customHeight="1">
+      <c r="A13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="15" t="s">
         <v>803</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="C13" s="15" t="s">
         <v>804</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="D13" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>805</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="15" t="s">
         <v>806</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+      <c r="G13" s="15" t="s">
+        <v>807</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
     </row>
-    <row r="14" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:10" ht="120" customHeight="1">
+      <c r="A14" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>807</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>808</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>756</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="C14" s="15" t="s">
         <v>809</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6" t="s">
+      <c r="D14" s="15" t="s">
+        <v>757</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>810</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="F14" s="15"/>
+      <c r="G14" s="15" t="s">
         <v>811</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="H14" s="15" t="s">
         <v>812</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="I14" s="15" t="s">
         <v>813</v>
       </c>
+      <c r="J14" s="15" t="s">
+        <v>814</v>
+      </c>
     </row>
-    <row r="15" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:10" ht="120" customHeight="1">
+      <c r="A15" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>814</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="B15" s="15" t="s">
         <v>815</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>756</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="C15" s="15" t="s">
         <v>816</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6" t="s">
+      <c r="D15" s="15" t="s">
+        <v>757</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>817</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="F15" s="15"/>
+      <c r="G15" s="15" t="s">
         <v>818</v>
       </c>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6" t="s">
+      <c r="H15" s="15" t="s">
         <v>819</v>
       </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15" t="s">
+        <v>820</v>
+      </c>
     </row>
-    <row r="16" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:10" ht="120" customHeight="1">
+      <c r="A16" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>820</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="B16" s="15" t="s">
         <v>821</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="C16" s="15" t="s">
         <v>822</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="D16" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>823</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="F16" s="15" t="s">
         <v>824</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6" t="s">
+      <c r="G16" s="15" t="s">
         <v>825</v>
       </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15" t="s">
+        <v>826</v>
+      </c>
     </row>
-    <row r="17" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:10" ht="120" customHeight="1">
+      <c r="A17" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>826</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="15" t="s">
         <v>827</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="C17" s="15" t="s">
         <v>828</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="15" t="s">
         <v>829</v>
       </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6" t="s">
+      <c r="E17" s="15" t="s">
         <v>830</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="F17" s="15"/>
+      <c r="G17" s="15" t="s">
         <v>831</v>
       </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6" t="s">
+      <c r="H17" s="15" t="s">
         <v>832</v>
       </c>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15" t="s">
+        <v>833</v>
+      </c>
     </row>
-    <row r="18" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:10" ht="120" customHeight="1">
+      <c r="A18" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>834</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="C18" s="15" t="s">
         <v>835</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6" t="s">
+      <c r="D18" s="15" t="s">
+        <v>829</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="F18" s="15"/>
+      <c r="G18" s="15" t="s">
         <v>837</v>
       </c>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6" t="s">
+      <c r="H18" s="15" t="s">
         <v>838</v>
       </c>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15" t="s">
+        <v>839</v>
+      </c>
     </row>
-    <row r="19" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:10" ht="120" customHeight="1">
+      <c r="A19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="C19" s="6" t="s">
+      <c r="B19" s="15" t="s">
         <v>840</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="C19" s="15" t="s">
         <v>841</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="D19" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>842</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="F19" s="15" t="s">
         <v>843</v>
       </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6" t="s">
+      <c r="G19" s="15" t="s">
         <v>844</v>
       </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15" t="s">
+        <v>845</v>
+      </c>
     </row>
-    <row r="20" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:10" ht="120" customHeight="1">
+      <c r="A20" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>845</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="B20" s="15" t="s">
         <v>846</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>737</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="C20" s="15" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6" t="s">
+      <c r="D20" s="15" t="s">
+        <v>738</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15" t="s">
+        <v>849</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
     </row>
-    <row r="21" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:10" ht="120" customHeight="1">
+      <c r="A21" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="B21" s="15" t="s">
         <v>850</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="C21" s="15" t="s">
         <v>851</v>
       </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6" t="s">
+      <c r="D21" s="15" t="s">
+        <v>829</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>852</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="F21" s="15"/>
+      <c r="G21" s="15" t="s">
         <v>853</v>
       </c>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
+      <c r="H21" s="15" t="s">
+        <v>854</v>
+      </c>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:J21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>